--- a/deliverables/复兴岛_全球创客岛_科创出海与具身智能国际大会_执行计划表.xlsx
+++ b/deliverables/复兴岛_全球创客岛_科创出海与具身智能国际大会_执行计划表.xlsx
@@ -9,43 +9,51 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.总览仪表盘" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.活动总览" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.历史文脉" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.领导寄托" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.规划与课题" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.择日专章" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.详细议程" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.黑客松专章" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.嘉宾邀请" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.一带一路国别池" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.揭牌落位" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.席位结构" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.组织架构" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.倒排期" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14.预算测算" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15.KPI成效" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16.风险预案" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17.下一步行动" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18.主题板块" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.活动结构" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.历史文脉" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.领导寄托" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.规划与课题" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.敦煌项目" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.冷启动角色" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.择日专章" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.详细议程" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.体验游戏层" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.黑客松专章" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.嘉宾邀请" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.一带一路国别池" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14.揭牌落位" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15.席位结构" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16.组织架构" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17.倒排期" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18.预算测算" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19.KPI成效" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20.风险预案" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21.下一步行动" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22.主题板块" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1.活动总览'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'2.历史文脉'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'3.领导寄托'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'4.规划与课题'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'5.择日专章'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'6.详细议程'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'7.黑客松专章'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'8.嘉宾邀请'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'9.一带一路国别池'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'10.揭牌落位'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'11.席位结构'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'12.组织架构'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'13.倒排期'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'14.预算测算'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'15.KPI成效'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'16.风险预案'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'17.下一步行动'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="18">'18.主题板块'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'2.活动结构'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'3.历史文脉'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'4.领导寄托'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'5.规划与课题'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'6.敦煌项目'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'7.冷启动角色'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'8.择日专章'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'9.详细议程'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'10.体验游戏层'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'11.黑客松专章'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'12.嘉宾邀请'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'13.一带一路国别池'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'14.揭牌落位'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'15.席位结构'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'16.组织架构'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'17.倒排期'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'18.预算测算'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'19.KPI成效'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">'20.风险预案'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">'21.下一步行动'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="22">'22.主题板块'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -204,6 +212,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -212,9 +223,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -584,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -596,14 +604,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2026 复兴岛·全球创客岛收官答卷大会｜Excel 执行呈现台账（V2）</t>
+          <t>2026 复兴岛·全球创客岛收官答卷大会｜Excel 执行呈现台账（V3）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>科创出海 × 人工智能 × 具身智能国际大会｜V2.0 · 建议稿｜Slogan：百年复兴，智造再启航｜主会日 2026-09-12</t>
+          <t>V3.0 · 建议稿｜主论坛+分论坛+体验层+黑客松｜敦煌意向｜主会日 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -649,7 +657,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>9/15前最近开市/挂匾吉日</t>
+          <t>服务9/15收官节点</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -661,154 +669,154 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>黑客松</t>
+          <t>活动结构</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>9/11晚–9/12下午</t>
+          <t>四层组合</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>船台·智能体 24h</t>
+          <t>主论坛+分论坛+体验层+黑客松</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>见黑客松专章</t>
+          <t>见活动结构</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>活动规模</t>
+          <t>敦煌意向</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>主会200–300人</t>
+          <t>2000㎡/净高9–11m</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>黑客松20–40队分流</t>
+          <t>壁画IP·沉浸·机器人·待核实950万</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>见席位结构</t>
+          <t>见敦煌项目</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>国际规格</t>
+          <t>黑客松</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>总领事≥6国</t>
+          <t>9/11晚–9/12下午</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>一带一路亲自出席</t>
+          <t>船台·智能体24h+文旅赛道</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>见嘉宾邀请</t>
+          <t>见黑客松专章</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>硬成果</t>
+          <t>活动规模</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>揭牌≥3个</t>
+          <t>主会200–300人</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>国家厅+片区厅</t>
+          <t>黑客松20–40队+体验层流动</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>见揭牌落位</t>
+          <t>见席位结构</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>文脉主线</t>
+          <t>国际规格</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>百年复兴，智造再启航</t>
+          <t>总领事≥6国</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>周家嘴→复兴→创客岛</t>
+          <t>一带一路亲自出席</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>见历史文脉</t>
+          <t>见嘉宾邀请</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>预算中值</t>
+          <t>硬成果</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>约70万元</t>
+          <t>揭牌≥3个</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>场地/券包置换可压至约50万</t>
+          <t>国家厅+片区厅+敦煌视进度</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>见预算测算</t>
+          <t>见揭牌落位</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>备选日期</t>
+          <t>角色原则</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09（三）</t>
+          <t>智库/顾问</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>工作日开市吉日</t>
+          <t>不承诺政策·一事一议·先调研</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>领导周六不便时</t>
+          <t>见冷启动角色</t>
         </is>
       </c>
     </row>
@@ -841,7 +849,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
+    <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>1.活动总览</t>
@@ -849,7 +857,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>名称/时间/主题/规格</t>
+          <t>名称/时间/结构/规格</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -863,20 +871,20 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
+    <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2.历史文脉</t>
+          <t>2.活动结构</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>时间轴·载体·衍生议题</t>
+          <t>四层结构与组合逻辑</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>文脉叙事依据</t>
+          <t>形式设计</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -885,357 +893,2113 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
+    <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>3.领导寄托</t>
+          <t>3.历史文脉</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>市/区领导要点与回应</t>
+          <t>时间轴·载体·衍生</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
+          <t>文脉依据</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>4.领导寄托</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>市/区要点与回应</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
           <t>政治口径</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>4.规划与课题</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>大上海/杨浦规划对齐+六课题</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>5.规划与课题</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>规划对齐+六课题</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>议题设计</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>5.择日专章</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>6.敦煌项目</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>意向/空间/核实/用法</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>一事一议样本</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>7.冷启动角色</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>原则+协同方</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>对接纪律</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>8.择日专章</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>首选/备选/规避</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>日期决策</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>6.详细议程</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>全天环节含文脉与Demo Day</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>9.详细议程</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>全天含分论坛D与体验层</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>现场脚本</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>7.黑客松专章</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>10.体验游戏层</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>五关卡集章任务</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>体验执行</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>11.黑客松专章</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>赛道/赛程/规则/KPI</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>创客执行</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>8.嘉宾邀请</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>12.嘉宾邀请</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>政要/领事/产业/创客</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>邀约台账</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>9.一带一路国别池</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>拟邀国家与合作侧重</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>13.一带一路国别池</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>拟邀国家</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>国际资源</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>10.揭牌落位</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>国家厅/片区厅/平台</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>14.揭牌落位</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>会客厅+敦煌意向</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>硬成果</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>11.席位结构</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>主会席别配置</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>15.席位结构</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>主会席别</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>会务排座</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>12.组织架构</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>含文脉组/黑客松组</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>16.组织架构</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>含智库/文旅/黑客松</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>分工责任</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>13.倒排期</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>T-50至T+14</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>17.倒排期</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>节点任务</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>进度表</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>14.预算测算</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>18.预算测算</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>分项费用</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>资金安排</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>15.KPI成效</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>19.KPI成效</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>验收标准</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>复盘依据</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>复盘</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>16.风险预案</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>风险对策等级</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>20.风险预案</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>风险对策</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>应急</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>17.下一步行动</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>本周拍板事项</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>21.下一步行动</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>含敦煌48h核查</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>立即执行</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="40" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>以百年「复兴」文脉为底色，以市委启动「全球创客岛」与「量子城市」寄托为上位牵引，在岛上举办一场 200–300 人国际化科创出海与具身智能大会，同步完成国际会议厅揭牌，并以「船台·智能体」黑客松把创客生态做实，形成可汇报、可传播、可复用的阶段性政绩答卷。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>以百年「复兴」文脉与「敦煌」级文化 IP 为双引擎，以 9 月 15 日前收官节点为政治死线，在岛上以「主论坛 + 分论坛 + 沉浸式体验/游戏层 + 黑客松」组合拳，完成成果发布、国际会客厅揭牌与高价值项目（含敦煌意向）一事一议展示，形成可汇报、可传播、可复用的冷启动答卷。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A39:D40"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A35:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>详细议程｜2026 年 9 月 12 日（星期六 · 农历八月初二）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>主论坛+四分论坛+体验层+黑客松Demo Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>时段</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>环节</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>内容要点</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>责任方</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>08:30–09:15</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>签到 · 体验层开放</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>文脉三幕展 + 集章任务开启；贵宾/领事接待</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>会务+体验层</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>09:15–09:25</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>开幕影像</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>文脉短片《百年复兴，智造再启航》；点题敦煌沉浸</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>宣传组</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>09:25–09:35</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>主持人开场</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>介绍四层结构：主论坛/分论坛/体验层/黑客松</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>主持人</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>09:35–09:50</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>区委/区政府主要领导致辞</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>回应市领导寄托与 9/15 节点答卷</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>区领导</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>09:50–10:00</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>市级部门或特邀致辞（视情）</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>量子城市/规划资源/科创政策呼应</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>特邀领导</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>10:00–10:10</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>「一带一路」领事代表致辞</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>国际合作与科技出海期待</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>总领事代表</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>10:10–10:35</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>主旨成果发布</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>创客岛进展、量子城市、具身智能、文旅科技意向样本</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>运营/专班</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>10:35–11:05</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>国际会议厅/会客厅揭牌</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>国家厅+片区厅揭牌、铭牌落位、文脉场景合影</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>区领导+领事</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>11:05–11:35</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>重点项目签约/意向</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>入岛企业、出海合作；敦煌等一事一议（视成熟度）</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>区商务/科委</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>11:35–12:00</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>集体合影 · 媒体发布</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>领导—领事—企业—创客代表同框</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>宣传组</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>上午</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>12:00–13:30</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>工作午宴/闭门交流（可选）</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>小范围深度沟通；黑客松初审；体验层轮转</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>外事+黑客松</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>13:30–15:00</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>分论坛 A：文脉·空间·量子城市</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>治江治城、遗存活化、空间智能课题</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>规划/科委</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>13:30–15:00</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>分论坛 B：具身智能与低空经济</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>实训平台、场景合作、产业链对接</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>产业专班</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>13:30–15:00</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>分论坛 C：科创出海圆桌</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>分国别对接桌：领事×出海企业</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>商务/外事</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>13:30–15:00</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>分论坛 D：敦煌·文旅科技沉浸</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>IP/空间/机器人互动/商业模型；一事一议路径</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>文旅+科企联</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>13:30–15:00</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>体验层/黑客松观摩</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>沉浸关卡限流体验；黑客松工位开放（限流）</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>体验+黑客松</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>15:00–15:20</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>茶歇 · 展示体验</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>具身演示、低空静态展、敦煌样片/短时体验</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>展示组</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>15:20–16:20</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Demo Day · 高端对话</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>黑客松决赛路演 + 「论坛×游戏化体验」复盘对话</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>主持+评委</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>16:20–16:50</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>颁奖与下一阶段行动</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>黑客松颁奖；百日行动/会客厅/敦煌跟进清单</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>专班</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>16:50–17:30</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>国际对接酒会</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>领事—企业—优胜创客—文旅方自由对接</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>会务组</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>体验 / 游戏层关卡设计（论坛×游戏化体验）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>非电竞：沉浸关卡+集章任务；与分论坛D（敦煌）、黑客松互相导流</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>关卡</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>责任组</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>关卡 1 · 文脉三幕</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>周家嘴—定海—复兴—创客岛图文/影像，集章起点</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>文脉展示组</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>待脚本</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>关卡 2 · 船台任务</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>船台/塔吊打卡问答或 AR 简任务，强化工业遗存记忆</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>文脉展示组</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>待脚本</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>关卡 3 · 敦煌沉浸</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>短时沉浸样片/限流体验或多媒体剧场（视空间进度）</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>文旅沉浸组</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>待脚本</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>关卡 4 · 智能体互动</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>具身机器人互动关，衔接黑客松与实训平台</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>文脉展示组</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>待脚本</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>关卡 5 · 出海线索</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>国别会客厅导览任务，引导至分论坛 C 与酒会对接</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>文脉展示组</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>待脚本</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>结算</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>集齐印章兑换伴手礼/体验券；优胜线索进入黑客松或招商线索库</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>文脉展示组</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>待脚本</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>「船台·智能体」复兴创客黑客松｜执行台账</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>在百年船台，写出下一代智能体｜2026 年 9 月 11 日（五）晚 — 9 月 12 日（六）下午（约 24 小时）｜20–40 支团队（高校/创客/初创，每队 3–5 人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>为何举办</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>直接回应市委「开展好活动、集聚创新创业人才」要求。</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>为何举办</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>呼应区方案鼓励大赛展会、OPC 社群与创客学院生态。</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>为何举办</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>把「全球创客岛」从发布会做成可感知的创客现场。</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>为何举办</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>文脉衍生：船台曾承载造船下海，今日承载智能体「下水」。</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>赛道</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>赛道 1 · 空间智能：城市治理大模型、时空数据应用、岛上场景助手</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>待发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>赛道</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>赛道 2 · 具身智能：机器人实景任务、人机协同、实训场课题</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>待发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>赛道</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>赛道 3 · 低空/无人系统：巡检、物流、应急或文旅低空应用原型</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>待发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>赛道</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>赛道 4 · 科创出海工具：跨境合规、多语言服务、海外获客与本地化工具</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>待发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>赛道</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>赛道 5 · 文旅智能体（可选）：敦煌/壁画叙事智能体、沉浸导览、机器人互动脚本</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>待发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>赛前 2 周发布课题包与岛上开放数据/API（脱敏）；现场也可自带题目但须贴合赛道。</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>提供算力代金/云资源、导师工位、工业遗存场地氛围与演示道具。</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>导师团：产业专家 + 入岛企业 + 高校导师；国际领事可参与点评（可选）。</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>产出：可演示原型 + 3 分钟路演 + 一页应用场景说明。</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>规则</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>激励：奖金/算力券/模型券/入孵绿色通道/会客厅对接名额；优胜项目周六 Demo Day 登主舞台。</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>赛程</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>9/11 18:30–19:30 报到开营 · 文脉短片 · 课题发布</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>赛程</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>9/11 19:30–22:30 组队确认 · 导师匹配 · 开工</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>赛程</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>9/11 22:30–次日 12:00 连续开发（夜间值守与安全预案）</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>赛程</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>9/12 12:00–13:30 提交截止 · 初审 · 午餐休整</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>赛程</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>9/12 15:20–16:20 Demo Day（主论坛复会环节，决赛队伍路演）</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>赛程</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>9/12 16:20–16:40 颁奖 · 入孵/券包意向授意</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>报名队伍 ≥30，完赛 ≥20</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>待验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>产生可演示原型 ≥15 个</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>待验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>意向入孵/场景合作 ≥5 项</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>待验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>青年人才线索入库 ≥80 人</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>待验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>场地</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>岛上老厂房创客空间 / 实训平台周边（与主会场分流）</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>会务保障组</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>待锁定</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>嘉宾分层与邀约目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>邀约对象</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>目标</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>确认状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>A 政要领导层</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>杨浦区委书记、区长（主致辞 / 揭牌）；分管副区长（科创 / 商务 / 建设 / 规划资源）；视情邀请市级相关部门（规划资源、科委、商务、外办）领导出席或书面致辞</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>抬升政治规格，形成区级主场答卷画面</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>B 国际领事层</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>「一带一路」重点国家驻沪总领事 6–10 位亲自出席；领团代表或总领事俱乐部相关协调机制支持邀约；国别推介与国际会议厅冠名国对应总领事优先出席揭牌</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>全球化规格与国际合作落位的核心背书</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>C 产业·学术·创客层</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>具身智能 / 机器人 / AI 大模型 / 低空经济领军企业；量子城市 / 空间智能实验室与高校创新联盟代表；入岛孵化器、基金；黑客松导师与优胜团队代表</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>内容专业度、项目签约与创客生态可见度</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>D 媒体与传播层</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>市级主流媒体、区融媒体中心；科技垂类与国际传播渠道；文脉短片、直播与短视频团队</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>领导可见、社会可感、国际可传</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1560,13 +3324,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1578,9 +3342,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>国际会议厅 / 会客厅揭牌落位计划</t>
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>国际会议厅 / 会客厅揭牌落位计划（含敦煌视进度）</t>
         </is>
       </c>
     </row>
@@ -1700,43 +3464,71 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>敦煌文旅科技意向仪式（视对接进度）</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>0–1 项</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>选址意向 / 框架合作备忘录；或仅作体验层打样不强制签约</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>高价值文旅科技一事一议样本；服务设计艺术岛与 9/15 展示节点。</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>谈判中</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>落位原则</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>· 先锁意向、再上仪式：揭牌对象须在活动前完成协议文本与空间确认。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>· 一国一厅、一厅一责：明确运营主体、年度活动频次与招商指标。</t>
+          <t>· 先锁意向、再上仪式：揭牌对象须在活动前完成协议文本与空间确认。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>· 外事合规：领事出席与冠名事项提前报区外办 / 市外办指导。</t>
+          <t>· 一国一厅、一厅一责：明确运营主体、年度活动频次与招商指标。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>· 文脉同框：揭牌背景尽量融入船台/塔吊/老厂房元素，形成独特视觉记忆。</t>
+          <t>· 外事合规：领事出席与冠名事项提前报区外办 / 市外办指导。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>· 文脉同框：揭牌背景尽量融入船台/塔吊/老厂房元素，形成独特视觉记忆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>· 媒体可感知：揭牌背板、铭牌、导视与文脉短片同步备妥。</t>
         </is>
@@ -1745,18 +3537,18 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A10:F10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1963,13 +3755,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1981,7 +3773,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>组织架构与职责（含文脉组/黑客松组）</t>
+          <t>组织架构与职责（含智库/文旅/黑客松）</t>
         </is>
       </c>
     </row>
@@ -2038,12 +3830,12 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>文脉展示组</t>
+          <t>智库顾问组</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>短片、展廊、船台动线、主视觉「船台×数字网格」</t>
+          <t>创客学院/云基地：调研摸底、一事一议建议、不直接承诺政策</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr"/>
@@ -2052,12 +3844,12 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>外事礼宾组</t>
+          <t>生态转化组</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>领事邀约、报批、接待、翻译、礼品与位次</t>
+          <t>科企联：活动操盘、大厂资源、招商转化、私域激活</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr"/>
@@ -2066,12 +3858,12 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>产业内容组</t>
+          <t>文脉展示组</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>嘉宾演讲、分论坛、路演筛选、签约文本</t>
+          <t>短片、展廊、船台动线、主视觉「船台×数字网格」</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr"/>
@@ -2080,12 +3872,12 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>黑客松组</t>
+          <t>文旅沉浸组</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>出题、招募、导师、场地值守、评审与转化</t>
+          <t>敦煌对接、体验/游戏层关卡、高净高空间踏勘</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr"/>
@@ -2094,12 +3886,12 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>空间落位组</t>
+          <t>外事礼宾组</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>会客厅选址装修、铭牌、揭牌流程、后续运营协议</t>
+          <t>领事邀约、报批、接待、翻译、礼品与位次</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr"/>
@@ -2108,12 +3900,12 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>宣传媒体组</t>
+          <t>产业内容组</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>主视觉、新闻通稿、直播、短视频、外宣口径</t>
+          <t>嘉宾演讲、分论坛 A–D、路演筛选、签约文本</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr"/>
@@ -2122,16 +3914,58 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>会务保障组</t>
+          <t>黑客松组</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>场地、安保、交通、医疗、餐饮、物料与应急</t>
+          <t>出题、招募、导师、场地值守、评审与转化</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>空间落位组</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>会客厅选址装修、铭牌、揭牌流程、后续运营协议</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>宣传媒体组</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>主视觉、新闻通稿、直播、短视频、外宣口径</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>会务保障组</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>场地、安保、交通、医疗、餐饮、物料与应急</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr"/>
+      <c r="D16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2142,7 +3976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2233,7 +4067,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>文脉展示组</t>
+          <t>文旅沉浸组</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -2483,7 +4317,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>黑客松组</t>
+          <t>文旅沉浸组</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -2501,7 +4335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2518,7 +4352,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>预算测算（示意，单位：万元）</t>
         </is>
@@ -2913,650 +4747,6 @@
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>预期成效与 KPI</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>维度</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>量化目标</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>实测结果（待填）</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>是否达标</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>政治规格</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>区委书记或区长出席；形成可呈报市级的成果专报</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>文脉呈现</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>文脉短片+展廊落地；领导视察动线含船台/工业肌理打卡点</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>国际出席</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>总领事亲自出席 ≥6 国；国际嘉宾可感知占比</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>揭牌落位</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>国家/片区国际会议厅揭牌 ≥3 个；配套运营协议签署</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>黑客松</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>完赛 ≥20 队；可演示原型 ≥15；意向转化 ≥5 项</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>产业成果</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>现场签约/发布 ≥8 项；覆盖 AI、具身、低空、出海至少三类</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>规模体验</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>主会场 200–300 人；无重大后勤与外事事故</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>传播声量</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>市级以上媒体报道 ≥5 篇；短视频与政务新媒体矩阵同步</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>后续转化</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>T+30 日内至少 1 场国别对接或优胜项目入孵跟进</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>风险预案</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>风险</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>对策</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>跟踪人</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>外事报批时限不足</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>立即按 9/12 倒排报批；同步准备 9/9 工作日预案</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>主要领导档期冲突</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>提前两周锁定；备选致辞领导与录像致辞方案</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>黑客松通宵安全与扰民</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>封闭园区值守、实名手环、医疗点、噪声管控</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>总领事出席人数不达预期</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>扩大邀约池；揭牌国必须本人到场</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>揭牌空间未完工</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>仪式性揭牌+过渡空间；铭牌可先落临时展陈区</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>文脉表达表面化</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>短片与展陈提前评审；避免只贴历史照片、无当代转译</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>涉外内容与口径风险</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>统一外宣口径；演讲稿预审；敏感议题禁入</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>周六动员难</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>机关值班制；以国际对接+黑客松激励企业与青年报名</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>下一步行动清单</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>行动项</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>完成时限</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>本周内：确认「9/12 主日期 + 9/9 备选」与正式命名（含黑客松品牌名）。</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>本周内</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>3 日内：成立专班（含文脉展示组、黑客松组），明确组长。</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>3日内</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>1 周内：锁定主会场、黑客松厂房与首批 3 个揭牌对象谈判文本。</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>1周内</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>10 日内：发出总领事邀约；黑客松赛题与报名页上线；启动外事报批。</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>10日内</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>同步：完成主视觉与「一页纸」请示件（附 PPT+Excel），供区主要领导决策。</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>同步推进</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>四大主题板块协同要点</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>板块</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>英文标签</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>要点</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>文脉续写与空间更新</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Heritage × Renewal</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>治江→治城：浚浦工程传统与量子城市治理对照；工业遗存轻度改造样本：船台公园与老厂房焕新；人民城市理念下的滨江公共空间与创客生活</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>科创出海</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Go Global</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>「一带一路」营商环境与科技合作机会；从「造船下海」到「智能装备/算法出海」；国家会客厅与双向投资、离岸孵化机制</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>人工智能与空间智能</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>AI × Quantum City</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>量子城市时空智能底座与城市治理大模型；模型即服务（MaaS）与真实场景训练迭代；算力券/模型券/语料券政策兑现案例</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>具身智能与低空经济</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Embodied × Low-alt</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>实景空间实验实训实测与「硅基岛民」示范；环水地理条件下的无人机/eVTOL/无人艇测试叙事；感知—决策—执行闭环与产业链协同</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3676,7 +4866,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>复兴岛核心启动区 / 船台公园及周边工业厂房会场</t>
+          <t>复兴岛核心启动区 / 船台公园及周边高净高工业厂房</t>
         </is>
       </c>
     </row>
@@ -3688,7 +4878,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>主会场 200–300 人；黑客松 20–40 支团队（约 80–160 人，可分流）</t>
+          <t>主会场 200–300 人；黑客松 20–40 队；体验层另计流动人次</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -3698,19 +4888,19 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>文脉续写 · 科创出海 · AI/具身智能/低空 · 创客黑客松</t>
+          <t>文脉续写 · 科创出海 · AI/具身/低空 · 敦煌文旅科技 · 黑客松</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>活动形式</t>
+          <t>活动结构</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>文脉展 + 主论坛 + 分论坛 + 揭牌签约 + 黑客松 Demo Day + 国际对接酒会</t>
+          <t>主论坛 + 四分论坛 + 体验/游戏层 + 黑客松（四层组合）</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3720,7 +4910,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>区委书记/区长出席；「一带一路」多国总领事出席；市级部门视情邀请</t>
+          <t>区委书记/区长出席；一带一路总领事；敦煌等一事一议样本</t>
         </is>
       </c>
     </row>
@@ -3732,16 +4922,736 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>成果发布 + 会客厅揭牌 + 项目签约 + 黑客松优胜落地 + 媒体传播</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
+          <t>成果发布 + 会客厅揭牌 + 项目意向/签约 + Demo Day + 沉浸体验打样</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>协同机制</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>创客学院/云基地智库顾问 + 科企联活动招商转化</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>预期成效与 KPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>量化目标</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>实测结果（待填）</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>是否达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>政治规格</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>区委书记或区长出席；形成可呈报市级的 9/15 节点成果专报</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>四层结构</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>主论坛+四分论坛+体验层+黑客松全部跑通，各层有可截取画面</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>文脉呈现</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>文脉短片+展廊+船台打卡；领导视察动线含工业肌理</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>敦煌样本</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>完成事实核查；形成一事一议建议或意向仪式/体验打样其一</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>国际出席</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>总领事亲自出席 ≥6 国；国际嘉宾可感知占比</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>揭牌落位</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>国家/片区国际会议厅揭牌 ≥3 个；配套运营协议签署</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>黑客松</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>完赛 ≥20 队；可演示原型 ≥15；意向转化 ≥5 项</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>产业成果</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>现场签约/发布 ≥8 项；覆盖 AI、具身、低空、出海、文旅至少三类</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>规模体验</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>主会场 200–300 人；体验层有序限流；无重大事故</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>传播声量</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>市级以上媒体报道 ≥5 篇；短视频与政务新媒体矩阵同步</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>后续转化</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>T+30 日内国别对接或敦煌/优胜项目跟进至少 1 场</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>风险预案</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>对策</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>跟踪人</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>外事报批时限不足</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>立即按 9/12 倒排报批；同步准备 9/9 工作日预案</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>主要领导档期冲突</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>提前两周锁定；备选致辞领导与录像致辞方案</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>黑客松通宵安全与扰民</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>封闭园区值守、实名手环、医疗点、噪声管控</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>总领事出席人数不达预期</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>扩大邀约池；揭牌国必须本人到场</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>揭牌空间未完工</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>仪式性揭牌+过渡空间；铭牌可先落临时展陈区</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>文脉表达表面化</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>短片与展陈提前评审；避免只贴历史照片、无当代转译</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>涉外内容与口径风险</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>统一外宣口径；演讲稿预审；敏感议题禁入</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>周六动员难</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>机关值班制；以国际对接+黑客松激励企业与青年报名</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>下一步行动清单（含敦煌 48h 核查）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>行动项</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>完成时限</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>本周内：确认「9/12 主日期 + 9/9 备选」与四层结构命名（含黑客松、体验层）。</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>本周内</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>对接会后 48 小时：输出敦煌事实核查表（950 万口径、空间、政策诉求、机器人能力）。</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>对接会后48小时</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>3 日内：踏勘候选 2000㎡ / 净高 9–11m 厂房，评估 9 月可呈现度（体验打样 or 仅路演）。</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>3日内</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>1 周内：成立专班（智库顾问组、生态转化组、文旅沉浸组、黑客松组），明确组长。</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>1周内</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>1 周内：锁定主会场、体验层/黑客松厂房与首批 3 个揭牌对象谈判文本。</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>1周内</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>10 日内：总领事邀约 + 黑客松报名上线 + 外事报批；敦煌达线则启动一事一议报区。</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>10日内</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>同步：完成主视觉与「一页纸」请示件（附 PPT+Excel），供区主要领导决策。</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>同步推进</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>四大主题板块协同要点（含敦煌沉浸）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>板块</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>英文标签</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>文脉续写与空间更新</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Heritage × Renewal</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>治江→治城：浚浦工程传统与量子城市治理对照；工业遗存轻度改造：船台公园与高净高厂房焕新；人民城市理念下的滨江公共空间与创客生活</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>科创出海</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Go Global</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>「一带一路」营商环境与科技合作机会；从「造船下海」到「智能装备/算法出海」；国家会客厅与双向投资、离岸孵化机制</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>人工智能 · 具身 · 低空</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>AI × Embodied × Low-alt</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>量子城市时空智能与城市治理大模型；具身智能实景实训与「硅基岛民」示范；环水条件下低空/无人系统应用试验</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>敦煌·文旅科技沉浸</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Dunhuang Immersive</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>壁画 IP × 机器人/智能体的沉浸叙事；约 2000㎡ / 净高 9–11m 产品基地空间议题；论坛讲解 + 体验关卡，服务设计艺术岛定位</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3754,415 +5664,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>历史文脉时间轴 · 载体 · 衍生议题</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>四层结构：主论坛 · 分论坛 · 体验/游戏层 · 黑客松</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>周家嘴浅滩→定海岛→复兴岛→全球创客岛｜资料依据公开权威信息整理</t>
+          <t>主论坛定调 · 分论坛深耕 · 体验层引流 · 黑客松出苗</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>时期</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>节点</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>要点</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>关键产出</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>清末—民初</t>
+          <t>L1 主论坛（上午）</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>周家嘴浅滩</t>
+          <t>政治规格与收官叙事：领导致辞、成果发布、会客厅揭牌、重点签约；定调「百年复兴，智造再启航」，敦煌等仅作文旅科技样本点题。</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>黄浦江左岸鱼嘴状浅滩，因周家嘴村得名；浚浦局启动航道整治。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
+          <t>领导画面/揭牌签约</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>1913—1934</t>
+          <t>L2 分论坛（下午平行）</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>吹填成岛</t>
+          <t>A 文脉·空间·量子城市；B 具身智能与低空；C 科创出海圆桌；D 敦煌·文旅科技与沉浸体验（新增）。专业深耕、可出纪要与对接清单。</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>抛柴排筑堤、吹泥填土，周家嘴岛基本形成；南北约 3.4 公里，面积约 1.13 平方公里。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
+          <t>专业纪要/对接清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1927 前后</t>
+          <t>L3 体验 / 游戏层（全天并行）</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>定海桥贯通</t>
+          <t>非电竞意义的「游戏」，而是可玩可感的沉浸关卡：文脉三幕展、船台打卡任务、敦煌沉浸短时体验、具身智能互动关、集章换礼/线索任务，把流量与年轻创客导入岛上场景。</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>定海路桥建成，岛与市区陆路连通；浚浦局工场、仓储起步。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+          <t>传播素材/年轻流量</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>1930 年代</t>
+          <t>L4 黑客松（9/11 晚—9/12）</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>工业岛成型</t>
+          <t>「船台·智能体」24h 开发；增设「文旅智能体/沉浸叙事」相关赛题可选；Demo Day 回归主舞台，与主论坛形成「发布—验证—出苗」闭环。</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>大中华造船机器厂、上海鱼市场等入驻；造船、仓储、能源产业集聚。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>1937—1945</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>定海岛岁月</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>日军占领后改称定海岛（一度昭和岛）；抗战胜利后更名「复兴岛」，寓国家复兴。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>解放后—本世纪</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>产业基地</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>燃料、木材、石油、仓储、造船、渔业等国央企扎根，见证民族工业荣光。</t>
+          <t>原型/人才线索</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>组合逻辑</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>战略留白期</t>
+          <t>逻辑1</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>留白岛</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>中心城区稀缺滨水战略空间，为未来城市实验预留；工业肌理与遗存得以保全。</t>
-        </is>
-      </c>
+          <t>主论坛负责「领导可见」；分论坛负责「专业可谈」；体验层负责「大众可感」；黑客松负责「青年可来」。</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2024.12 起</t>
+          <t>逻辑2</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>量子城市场</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>上海量子城市时空智能创新基地启动，岛上感知、语料与场景底座起步。</t>
-        </is>
-      </c>
+          <t>敦煌既可进分论坛讲模式，也可进体验层做沉浸，形成「论坛+游戏化体验」组合。</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>2025.12.18</t>
+          <t>逻辑3</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>全球创客岛</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>市委书记陈吉宁调研并启动「上海复兴岛—全球创客岛」，岛正式进入开局年。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>2026.02</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>集聚区方案</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>杨府发〔2026〕1 号印发，锚定三岛定位与四大产业方向，政策体系成型。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>文脉载体</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>载体</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>活动用法</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>船台公园（共青路 130 号）</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>沪东中华造船厂旧址；保留船台斜率、1973 年 120 吨塔吊与厂区道路肌理；量子城市时空创新基地重要载体。</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>视察打卡/室外合影</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>定海路桥（定海桥）</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>1927 年钢筋混凝土桥，曾是连通市区的唯一陆路通道；岛城关系的历史符号。</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>开幕影像符号</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>白庐 / 复兴岛公园</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>浚浦局职员俱乐部旧址与公园绿地；近代工程管理与生活记忆的空间标本。</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>展廊节点</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>存量工业厂房（约 30 万㎡）</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>先期盘活约 5 万㎡老厂房为共享实验室、概念验证中心、中试基地与创客空间。</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>黑客松与分论坛场地</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>复兴岛运河</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>筑岛同期疏浚形成的人工水道；环水地理环境支撑低空/无人艇等测试叙事。</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>低空/无人艇叙事</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>衍生议题</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>衍生方向</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>要点1</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>要点2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>议题衍生：从「浚浦治江」到「量子治城」</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>百年前以工程力量疏浚黄浦、吹填成岛；今天以时空智能治理超大城市。</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>主论坛设置「治江—治城」对照叙事，突出上海治理传统的时代升级。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>议题衍生：从「造船下海」到「科创出海」</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>大中华/中华造船的下海基因，映射今日 AI、具身智能、低空装备的全球化。</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>国别推介与会客厅揭牌，延续「面江向海」的开放传统。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>议题衍生：从「工业遗存」到「创新资产」</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>轻度改造、保护肌理——呼应市委「盘活用好工业建筑、注重保护原有肌理」。</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>成果展廊设「船台—塔吊—智能体」三幕叙事，供领导视察与媒体拍摄。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>议题衍生：从「定海/复兴」到「再复兴」</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>岛名本身即政治象征：抗战胜利后定名「复兴」，今日再以创客与智能复兴。</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>活动主视觉可用「船台曲线 × 数字网格」，口号建议：「百年复兴，智造再启航」。</t>
-        </is>
-      </c>
+          <t>冷启动阶段以打样为主：先做出 1–2 个可传播场景，再谈重资产永久落地。</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4180,280 +5843,430 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>市、区领导寄托与活动回应</t>
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>历史文脉时间轴 · 载体 · 衍生议题</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>把领导讲话转译为可执行的活动模块</t>
+          <t>周家嘴浅滩→定海岛→复兴岛→全球创客岛｜含敦煌衍生</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>时期</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>要点</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>本场回应模块</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
+    </row>
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>市委书记陈吉宁（2025-12-18 调研及启动大会）</t>
+          <t>清末—民初</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>坚持以规划为引领，把复兴岛打造为科技创新策源的活力新空间。</t>
+          <t>周家嘴浅滩</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>用大会回应「开展好活动」——高规格主论坛 + 国际揭牌 + 黑客松，三者齐备。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
+          <t>黄浦江左岸鱼嘴状浅滩，因周家嘴村得名；浚浦局启动航道整治。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>市委书记陈吉宁（2025-12-18 调研及启动大会）</t>
+          <t>1913—1934</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>盘活用好见证城市发展历史的工业建筑，注重保护原有肌理，注入创新创业功能。</t>
+          <t>吹填成岛</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>用展陈回应「保护肌理、注入功能」——船台/塔吊视察动线 + 智能体演示同场。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
+          <t>抛柴排筑堤、吹泥填土，周家嘴岛基本形成；南北约 3.4 公里，面积约 1.13 平方公里。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>市委书记陈吉宁（2025-12-18 调研及启动大会）</t>
+          <t>1927 前后</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>搭建好平台、组织好培训、开展好活动，更好吸引集聚创新创业人才。</t>
+          <t>定海桥贯通</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>用政策发布回应「低成本、高效率、便利性」——券包、公寓、入岛通道现场兑现案例。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
+          <t>定海路桥建成，岛与市区陆路连通；浚浦局工场、仓储起步。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>市委书记陈吉宁（2025-12-18 调研及启动大会）</t>
+          <t>1930 年代</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>着眼低成本、高效率、便利性，优化配置创新创业资源要素，与全球创客同频共振。</t>
+          <t>工业岛成型</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>用场景测试回应「试出经验、试出路径」——具身智能/低空/空间智能课题路演与签约。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
+          <t>大中华造船机器厂、上海鱼市场等入驻；造船、仓储、能源产业集聚。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>市委书记陈吉宁（2025-12-18 调研及启动大会）</t>
+          <t>1937—1945</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>围绕人工智能赋能城市空间治理，在具体场景测试应用中试出经验、试出路径。</t>
+          <t>定海岛岁月</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>用创客黑客松回应「吸引集聚人才」——青年团队 24 小时登岛出作品、出项目苗子。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
+          <t>日军占领后改称定海岛（一度昭和岛）；抗战胜利后更名「复兴岛」，寓国家复兴。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>市委书记陈吉宁（2025-12-18 调研及启动大会）</t>
+          <t>解放后—本世纪</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>深化科技赋能、增强科创动能、培育创业生态，探索超大城市空间治理新路子。</t>
+          <t>产业基地</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>用大会回应「开展好活动」——高规格主论坛 + 国际揭牌 + 黑客松，三者齐备。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
+          <t>燃料、木材、石油、仓储、造船、渔业等国央企扎根，见证民族工业荣光。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>市委、市政府工作部署（量子城市与实验基地）</t>
+          <t>战略留白期</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>复兴岛作为上海量子城市实验基地、时空智能创新先行区。</t>
+          <t>留白岛</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>用展陈回应「保护肌理、注入功能」——船台/塔吊视察动线 + 智能体演示同场。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
+          <t>中心城区稀缺滨水战略空间，为未来城市实验预留；工业肌理与遗存得以保全。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>市委、市政府工作部署（量子城市与实验基地）</t>
+          <t>2024.12 起</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>目标愿景：未来城市实验区、创新创业和人才集聚区、时空智能创新先行区。</t>
+          <t>量子城市场</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>用政策发布回应「低成本、高效率、便利性」——券包、公寓、入岛通道现场兑现案例。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
+          <t>上海量子城市时空智能创新基地启动，岛上感知、语料与场景底座起步。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>市委、市政府工作部署（量子城市与实验基地）</t>
+          <t>2025.12.18</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>黄浦江中北段打造具有世界影响力的科创高地、创新创业集聚区与高品质水岸。</t>
+          <t>全球创客岛</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>用场景测试回应「试出经验、试出路径」——具身智能/低空/空间智能课题路演与签约。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
+          <t>市委书记陈吉宁调研并启动「上海复兴岛—全球创客岛」，岛正式进入开局年。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>杨浦区委区政府（三岛定位与集聚区方案）</t>
+          <t>2026.02</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>锚定「数字智能岛、设计艺术岛、人民城市岛」新使命。</t>
+          <t>集聚区方案</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>用创客黑客松回应「吸引集聚人才」——青年团队 24 小时登岛出作品、出项目苗子。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>杨浦区委区政府（三岛定位与集聚区方案）</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>以约 30 万㎡存量工业建筑、约 2500 间人才公寓为禀赋，打造国际创新创业集聚区。</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>用大会回应「开展好活动」——高规格主论坛 + 国际揭牌 + 黑客松，三者齐备。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>杨浦区委区政府（三岛定位与集聚区方案）</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>功能导向：低成本、高效率、便利性；先期盘活约 5 万㎡老厂房。</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>用展陈回应「保护肌理、注入功能」——船台/塔吊视察动线 + 智能体演示同场。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>杨浦区委区政府（三岛定位与集聚区方案）</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>政策工具：创新券、算力券、模型券、语料券；创客学院、高校创新联盟、OPC 社群。</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>用政策发布回应「低成本、高效率、便利性」——券包、公寓、入岛通道现场兑现案例。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>杨浦区委区政府（三岛定位与集聚区方案）</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>举办国际顶尖峰会、大赛展会与社群活动，培育多元化、超活力、自生长创客集群。</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>用场景测试回应「试出经验、试出路径」——具身智能/低空/空间智能课题路演与签约。</t>
+          <t>杨府发〔2026〕1 号印发，锚定三岛定位与四大产业方向，政策体系成型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>文脉载体</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>载体</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>活动用法</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>船台公园（共青路 130 号）</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>沪东中华造船厂旧址；保留船台斜率、1973 年 120 吨塔吊与厂区道路肌理；量子城市时空创新基地重要载体。</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>视察打卡/室外合影</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>定海路桥（定海桥）</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>1927 年钢筋混凝土桥，曾是连通市区的唯一陆路通道；岛城关系的历史符号。</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>开幕影像符号</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>白庐 / 复兴岛公园</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>浚浦局职员俱乐部旧址与公园绿地；近代工程管理与生活记忆的空间标本。</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>展廊节点</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>存量工业厂房（约 30 万㎡）</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>先期盘活约 5 万㎡老厂房为共享实验室、概念验证中心、中试基地与创客空间。</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>黑客松与分论坛场地</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>复兴岛运河</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>筑岛同期疏浚形成的人工水道；环水地理环境支撑低空/无人艇等测试叙事。</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>低空/无人艇叙事</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>衍生议题</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>衍生方向</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>要点1</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>要点2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>议题衍生：从「浚浦治江」到「量子治城」</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>百年前以工程力量疏浚黄浦、吹填成岛；今天以时空智能治理超大城市。</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>主论坛设置「治江—治城」对照叙事，突出上海治理传统的时代升级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>议题衍生：从「造船下海」到「科创出海」</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>大中华/中华造船的下海基因，映射今日 AI、具身智能、低空装备的全球化。</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>国别推介与会客厅揭牌，延续「面江向海」的开放传统。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>议题衍生：从「工业遗存」到「创新资产」</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>轻度改造、保护肌理——呼应市委「盘活用好工业建筑、注重保护原有肌理」。</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>成果展廊设「船台—塔吊—智能体」三幕叙事，供领导视察与媒体拍摄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>议题衍生：从「定海/复兴」到「再复兴」</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>岛名本身即政治象征：抗战胜利后定名「复兴」，今日再以创客与智能复兴。</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>活动主视觉可用「船台曲线 × 数字网格」，口号建议：「百年复兴，智造再启航」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>议题衍生：从「壁画文明」到「岛上沉浸」——敦煌 × 复兴岛</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>敦煌壁画 IP 与复兴岛「设计艺术岛」高度契合，可做文旅科技永久落地样本。</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>沉浸式剧目/机器人互动构成「体验层」，与主论坛形成「听故事—进场景」闭环。</t>
         </is>
       </c>
     </row>
@@ -4476,260 +6289,277 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>大上海 / 杨浦规划对齐与六大课题</t>
+          <t>市、区领导寄托与活动回应</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>杨府发〔2026〕1号 · 量子城市 · 规划资源指导意见 · 黄浦江中北段</t>
+          <t>把领导讲话转译为可执行的活动模块</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>规划维度</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>对齐要点</t>
+          <t>要点</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>活动落点</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
+          <t>本场回应模块</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>市级战略空间</t>
+          <t>市委书记陈吉宁（2025-12-18 调研及启动大会）</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>黄浦江中北段科创高地与高品质水岸；复兴岛为中心城区稀缺滨水战略空间与「留白」转化样板。</t>
+          <t>坚持以规划为引领，把复兴岛打造为科技创新策源的活力新空间。</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>主旨发布</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
+          <t>用大会回应「开展好活动」——高规格主论坛 + 国际揭牌 + 黑客松，三者齐备。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>量子城市行动</t>
+          <t>市委书记陈吉宁（2025-12-18 调研及启动大会）</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>时空智能创新基地 → 实验基地愿景行动 → 岛上全息空间智能体与感知终端；大会设置成果发布专章。</t>
+          <t>盘活用好见证城市发展历史的工业建筑，注重保护原有肌理，注入创新创业功能。</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>成果专章</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
+          <t>用展陈回应「保护肌理、注入功能」——船台/塔吊视察动线 + 智能体演示同场。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>规划资源新政</t>
+          <t>市委书记陈吉宁（2025-12-18 调研及启动大会）</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2025-12-17《支持复兴岛打造国际创新创业集聚区的规划资源指导意见》：综合发展区、过渡型综合利用、短期用地机制。</t>
+          <t>搭建好平台、组织好培训、开展好活动，更好吸引集聚创新创业人才。</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>政策发布</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
+          <t>用政策发布回应「低成本、高效率、便利性」——券包、公寓、入岛通道现场兑现案例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>杨浦实施方案</t>
+          <t>市委书记陈吉宁（2025-12-18 调研及启动大会）</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>杨府发〔2026〕1 号：四大产业方向 + 六大支持政策 + 市区分层协调、创客学院、高校创新联盟。</t>
+          <t>着眼低成本、高效率、便利性，优化配置创新创业资源要素，与全球创客同频共振。</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>产业分论坛</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
+          <t>用场景测试回应「试出经验、试出路径」——具身智能/低空/空间智能课题路演与签约。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>存量盘活机制</t>
+          <t>市委书记陈吉宁（2025-12-18 调研及启动大会）</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>产业用地综合绩效评估、国企「四个一批」、轻度改造保护工业文脉；船台公园已验证「遗存→资产」。</t>
+          <t>围绕人工智能赋能城市空间治理，在具体场景测试应用中试出经验、试出路径。</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>船台动线</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
+          <t>用创客黑客松回应「吸引集聚人才」——青年团队 24 小时登岛出作品、出项目苗子。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>人民城市理念</t>
+          <t>市委书记陈吉宁（2025-12-18 调研及启动大会）</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>数字智能 × 设计艺术 × 人民城市三岛一体；滨江公共空间、文体活动与创客生活同步呈现。</t>
+          <t>深化科技赋能、增强科创动能、培育创业生态，探索超大城市空间治理新路子。</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>人民城市展陈</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>课题编号</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>题目</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>聚焦内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>课题 A</t>
+          <t>用大会回应「开展好活动」——高规格主论坛 + 国际揭牌 + 黑客松，三者齐备。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>市委、市政府工作部署（量子城市与实验基地）</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>复兴岛作为上海量子城市实验基地、时空智能创新先行区。</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>用展陈回应「保护肌理、注入功能」——船台/塔吊视察动线 + 智能体演示同场。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>市委、市政府工作部署（量子城市与实验基地）</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>目标愿景：未来城市实验区、创新创业和人才集聚区、时空智能创新先行区。</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>用政策发布回应「低成本、高效率、便利性」——券包、公寓、入岛通道现场兑现案例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>市委、市政府工作部署（量子城市与实验基地）</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>百年复兴的空间哲学</t>
+          <t>黄浦江中北段打造具有世界影响力的科创高地、创新创业集聚区与高品质水岸。</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>文脉保护、轻度改造、过渡型综合利用如何服务创客岛</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>课题 B</t>
+          <t>用场景测试回应「试出经验、试出路径」——具身智能/低空/空间智能课题路演与签约。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>杨浦区委区政府（三岛定位与集聚区方案）</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>量子城市岛上答卷</t>
+          <t>锚定「数字智能岛、设计艺术岛、人民城市岛」新使命。</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>空间智能成果、场景清单、可复制治理经验</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>课题 C</t>
+          <t>用创客黑客松回应「吸引集聚人才」——青年团队 24 小时登岛出作品、出项目苗子。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>杨浦区委区政府（三岛定位与集聚区方案）</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>具身智能实景落地</t>
+          <t>以约 30 万㎡存量工业建筑、约 2500 间人才公寓为禀赋，打造国际创新创业集聚区。</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>实训平台成果、规则公约、企业场景合作</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>课题 D</t>
+          <t>用大会回应「开展好活动」——高规格主论坛 + 国际揭牌 + 黑客松，三者齐备。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>杨浦区委区政府（三岛定位与集聚区方案）</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>低空与未来出行试验</t>
+          <t>功能导向：低成本、高效率、便利性；先期盘活约 5 万㎡老厂房。</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>空域/水道测试、应用示范、安全与标准</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>课题 E</t>
+          <t>用展陈回应「保护肌理、注入功能」——船台/塔吊视察动线 + 智能体演示同场。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>杨浦区委区政府（三岛定位与集聚区方案）</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>科创出海与会客厅</t>
+          <t>政策工具：创新券、算力券、模型券、语料券；创客学院、高校创新联盟、OPC 社群。</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>国别机会、揭牌运营、企业对接闭环</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>课题 F</t>
+          <t>用政策发布回应「低成本、高效率、便利性」——券包、公寓、入岛通道现场兑现案例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>杨浦区委区政府（三岛定位与集聚区方案）</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>创客生态与黑客松</t>
+          <t>举办国际顶尖峰会、大赛展会与社群活动，培育多元化、超活力、自生长创客集群。</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>青年人才、OPC 社群、项目苗子孵化转化</t>
+          <t>用场景测试回应「试出经验、试出路径」——具身智能/低空/空间智能课题路演与签约。</t>
         </is>
       </c>
     </row>
@@ -4749,165 +6579,270 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>择日专章｜9/15 前最靠近收官节点的黄道吉日</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>大上海 / 杨浦规划对齐与六大课题</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>主推9/12；备选9/9；规避9/10杨公忌日；黑客松绑定周五晚开营</t>
+          <t>杨府发〔2026〕1号 · 量子城市 · 规划资源指导意见 · 含敦煌课题</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>宜/要点</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>决策建议</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>规划维度</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>对齐要点</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>活动落点</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>首选</t>
+          <t>市级战略空间</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026 年 9 月 12 日（星期六 · 农历八月初二）</t>
+          <t>黄浦江中北段科创高地与高品质水岸；复兴岛为中心城区稀缺滨水战略空间与「留白」转化样板。</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>开市·挂匾·立券·交易·出行</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>主推，最靠近9/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>主旨发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>黑客松窗口</t>
+          <t>量子城市行动</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026 年 9 月 11 日（五）晚 — 9 月 12 日（六）下午（约 24 小时）</t>
+          <t>时空智能创新基地 → 实验基地愿景行动 → 岛上全息空间智能体与感知终端；大会设置成果发布专章。</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>创客夜→答卷日</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>与主会绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>成果专章</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>备选一</t>
+          <t>规划资源新政</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026 年 9 月 9 日（星期三 · 农历七月廿八）</t>
+          <t>2025-12-17《支持复兴岛打造国际创新创业集聚区的规划资源指导意见》：综合发展区、过渡型综合利用、短期用地机制。</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>开市·交易·立券·出行</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>工作日备选</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>政策发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>备选二</t>
+          <t>杨浦实施方案</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026 年 9 月 3 日（星期四 · 农历七月廿二）</t>
+          <t>杨府发〔2026〕1 号：四大产业方向 + 六大支持政策 + 市区分层协调、创客学院、高校创新联盟。</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>金匮黄道日</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>预热/路演</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>产业分论坛</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>规避</t>
+          <t>存量盘活机制</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>产业用地综合绩效评估、国企「四个一批」、轻度改造保护工业文脉；船台公园已验证「遗存→资产」。</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>杨公忌日</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>不安排主会</t>
+          <t>船台动线</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>人民城市理念</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>数字智能 × 设计艺术 × 人民城市三岛一体；滨江公共空间、文体活动与创客生活同步呈现。</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>人民城市展陈</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>课题编号</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>题目</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>聚焦内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>课题 A</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>百年复兴的空间哲学</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>文脉保护、轻度改造、过渡型综合利用</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>课题 B</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>量子城市岛上答卷</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>空间智能成果、场景清单、可复制治理经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>课题 C</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>具身智能与低空试验</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>实训平台、空域水道测试、产业链协同</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>课题 D</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>科创出海与会客厅</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>国别机会、揭牌运营、企业对接闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>课题 E</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>敦煌文旅科技落岛</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>IP 授权、高净高空间、沉浸商业与一事一议</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>课题 F</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>创客生态与黑客松</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>青年人才、OPC 社群、体验层导流与转化</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4920,675 +6855,429 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>详细议程｜2026 年 9 月 12 日（星期六 · 农历八月初二）</t>
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>「敦煌」文旅科技项目（意向落户）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>含文脉开幕、揭牌签约、分论坛、黑客松Demo Day</t>
+          <t>意向对接中 · 建议纳入 9/12 活动一事一议展示与分论坛/体验层</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>时段</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>环节</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>内容要点</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>责任方</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>核实状态</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>上午</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>08:30–09:15</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>签到 · 文脉展廊开放</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>「周家嘴—复兴—创客岛」三幕展；贵宾/领事接待</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>会务+宣传</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
+          <t>基本面</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>发起：拥有敦煌壁画 IP 授权的国企背景项目方。</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>已同步</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>文旅沉浸组</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>上午</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>09:15–09:25</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>开幕影像</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>60–90 秒文脉短片《百年复兴，智造再启航》</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>宣传组</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
+          <t>基本面</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>市场信号：曾在「样立方」剧场开展剧播/沉浸活动；对外称约 10 天门票收益约 950 万元——该数据须在对接会上向项目方核实（票价、上座率、核算口径），本稿标注「待核实」。</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>待核实</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>文旅沉浸组</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>上午</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>09:25–09:35</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>主持人开场</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>介绍出席领导、国际嘉宾与黑客松并行安排</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>主持人</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+          <t>基本面</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>产品形态：沉浸式体验 + 机器人等科技互动；希望从短期活动升级为长期实体落地。</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>已同步</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>文旅沉浸组</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>上午</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>09:35–09:50</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>区委/区政府主要领导致辞</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>回应市领导寄托，发布阶段性答卷与下一步</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>区领导</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
+          <t>基本面</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>空间诉求：约 2000㎡；建筑净高 9–11m；意向地杨浦·复兴岛，作未来产品基地。</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>已同步</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>文旅沉浸组</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>上午</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>09:50–10:00</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>市级部门或特邀致辞（视情）</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>量子城市/规划资源/科创政策呼应</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>特邀领导</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+          <t>基本面</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>诉求重点：空间选址 + 文创/产业政策支持；项目方主动提出落户，落地意愿强。</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>已同步</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>文旅沉浸组</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>上午</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>10:00–10:10</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>「一带一路」领事代表致辞</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>国际合作与科技出海期待</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>总领事代表</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>契合点</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>与「设计艺术岛」定位高度契合，补齐文旅科技与沉浸体验短板。</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>共识</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>智库顾问组</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>上午</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>10:10–10:35</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>主旨成果发布</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>创客岛进展、量子城市岛上成果、具身智能平台、文脉活化样本</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>运营/专班</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+          <t>契合点</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>与工业遗存大空间（高净高厂房）天然匹配，可做轻度改造样本。</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>共识</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>智库顾问组</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>上午</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>10:35–11:05</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>国际会议厅/会客厅揭牌</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>国家厅+片区厅揭牌、铭牌落位、文脉场景合影</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>区领导+领事</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
+          <t>契合点</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>可与具身智能/机器人赛道交叉，形成「壁画 IP × 智能体」传播点。</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>共识</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>智库顾问组</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>上午</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>11:05–11:35</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>重点项目签约</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>入岛企业、出海合作、场景应用、创客生态协议</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>区商务/科委</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
+          <t>契合点</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>若在 9/12 前后完成意向仪式或体验打样，可直接服务 9/15 成果展示节点。</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>共识</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>智库顾问组</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>上午</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>11:35–12:00</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>集体合影 · 媒体发布</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>领导—领事—企业—创客代表同框</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>宣传组</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+          <t>活动用法</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>主论坛：作为「高价值文旅科技入岛」一事一议案例亮相（不作未核实数据背书）。</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>待脚本</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>产业内容组</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>上午</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>12:00–13:30</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>工作午宴/闭门交流（可选）</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>小范围深度沟通；黑客松同步初审</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>外事+黑客松组</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
+          <t>活动用法</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>分论坛 D：敦煌·文旅科技与沉浸体验专场（IP 授权、空间改造、机器人互动、商业模型）。</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>待脚本</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>产业内容组</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>13:30–15:00</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>分论坛 A：文脉·空间·量子城市</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>治江治城、遗存活化、空间智能课题</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>规划/科委</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
+          <t>活动用法</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>体验/游戏层：设置限流沉浸打卡或短时体验场（视空间进度；未完工则用多媒体+样片）。</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>待脚本</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>产业内容组</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>13:30–15:00</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>分论坛 B：具身智能与低空经济</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>实训平台、场景合作、产业链对接</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>产业专班</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
+          <t>活动用法</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>签约/备忘：若对接成熟，可安排框架合作/选址意向签署；不成则保留调研结论。</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>待脚本</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>产业内容组</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>13:30–15:00</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>分论坛 C：科创出海圆桌</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>分国别对接桌：领事×出海企业</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>商务/外事</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
+          <t>下一步</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>云基地代表与敦煌方初步交流，摸清合作诉求与空间/政策清单。</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>生态转化组</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>13:30–15:00</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>黑客松工位开放观摩</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>媒体与嘉宾参观开发现场（限流）</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
+          <t>下一步</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>核实「样立方」收益口径与可持续运营模型，形成一页事实核查表。</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>生态转化组</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>15:00–15:20</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>茶歇 · 展示体验</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>具身演示、低空静态展、文脉打卡点</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>展示组</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
+          <t>下一步</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>现场踏勘候选 2000㎡ / 净高 9–11m 厂房，评估改造周期与 9 月可呈现度。</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>生态转化组</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>15:20–16:20</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Demo Day · 高端对话</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>黑客松决赛路演 + 政产学研国际对话</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>主持+评委</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>16:20–16:50</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>颁奖与下一阶段行动</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>黑客松颁奖；百日行动/会客厅运营/创客日历发布</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>专班</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>下午</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>16:50–17:30</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>国际对接酒会</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>领事—企业—优胜创客自由对接</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>会务组</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
+          <t>下一步</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>符合高价值标准则启动一事一议报区；同步纳入大会分论坛与体验层脚本。</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>生态转化组</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5601,583 +7290,208 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>「船台·智能体」复兴创客黑客松｜执行台账</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>冷启动原则与协同角色</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>在百年船台，写出下一代智能体｜2026 年 9 月 11 日（五）晚 — 9 月 12 日（六）下午（约 24 小时）｜20–40 支团队（高校/创客/初创，每队 3–5 人）</t>
+          <t>智库/顾问定位 · 一事一议 · 先调研后成交 · 不直接承诺政策</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>类别</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>负责人</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>为何举办</t>
-        </is>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>原则</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>执行要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>直接回应市委「开展好活动、集聚创新创业人才」要求。</t>
+          <t>复兴岛仍处冷启动：可用载体多已被认领，入驻政策口径尚不清晰，规则由创客学院等机制逐步定。</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>为何举办</t>
-        </is>
+          <t>对接纪律</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>呼应区方案鼓励大赛展会、OPC 社群与创客学院生态。</t>
+          <t>领导层高度关注 9 月 15 日建设成果展示节点——一切可呈现的活动与成果须快速响应。</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>为何举办</t>
-        </is>
+          <t>对接纪律</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>把「全球创客岛」从发布会做成可感知的创客现场。</t>
+          <t>定位为「智库 / 顾问」：非业主、非政府决策主体，不直接承诺政策，但积极调研、建议与撮合。</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>为何举办</t>
-        </is>
+          <t>对接纪律</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>文脉衍生：船台曾承载造船下海，今日承载智能体「下水」。</t>
+          <t>高价值项目走「一事一议」直报区领导；一般项目先调研摸底，不强行成交。</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>赛道</t>
-        </is>
+          <t>对接纪律</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>赛道 1 · 空间智能：城市治理大模型、时空数据应用、岛上场景助手</t>
+          <t>核心动作：摸清各方需求与市场情报，筛出与岛气质匹配的项目，寻找互利共赢机会。</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>待发布</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>赛道</t>
-        </is>
+          <t>对接纪律</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>赛道 2 · 具身智能：机器人实景任务、人机协同、实训场课题</t>
+          <t>人脉即资产：需高频激活、打标签、形成价值链；用活动与场景让资源流动起来。</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>待发布</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>赛道</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>赛道 3 · 低空/无人系统：巡检、物流、应急或文旅低空应用原型</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>待发布</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>赛道</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>赛道 4 · 科创出海工具：跨境合规、多语言服务、海外获客与本地化工具</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>待发布</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>规则</t>
+          <t>对接纪律</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>角色方</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>价值与职责</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>杨浦区科技企业联合会（胡继刚等）</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>赛前 2 周发布课题包与岛上开放数据/API（脱敏）；现场也可自带题目但须贴合赛道。</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>规则</t>
+          <t>执行会长资源；低成本办会、大厂论坛、AI 活动操盘；上万私域人脉；上半年招商落地约 2700㎡ 案例；东南亚领事出海论坛等生态协同。</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>上海云基地 / 复兴岛运营协同方</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>提供算力代金/云资源、导师工位、工业遗存场地氛围与演示道具。</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>规则</t>
+          <t>地理与垂直生态优势；创客学院草创期「化缘」与合规付费原则；授权一线对接、调研摸底；强调合作「明明白白」、先试点再深聊。</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>创客学院（规则与生态）</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>导师团：产业专家 + 入岛企业 + 高校导师；国际领事可参与点评（可选）。</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>规则</t>
+          <t>负责逐步明确入驻与活动规则；叠加「未来城市创新实验」方向：方案孵化、产学研联动；把偶然需求打样为可复制案例。</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>敦煌项目方（意向入岛）</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>产出：可演示原型 + 3 分钟路演 + 一页应用场景说明。</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>规则</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>激励：奖金/算力券/模型券/入孵绿色通道/会客厅对接名额；优胜项目周六 Demo Day 登主舞台。</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>赛程</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>9/11 18:30–19:30 报到开营 · 文脉短片 · 课题发布</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>赛程</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>9/11 19:30–22:30 组队确认 · 导师匹配 · 开工</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>赛程</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>9/11 22:30–次日 12:00 连续开发（夜间值守与安全预案）</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>赛程</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>9/12 12:00–13:30 提交截止 · 初审 · 午餐休整</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>赛程</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>9/12 15:20–16:20 Demo Day（主论坛复会环节，决赛队伍路演）</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>赛程</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>9/12 16:20–16:40 颁奖 · 入孵/券包意向授意</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>报名队伍 ≥30，完赛 ≥20</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>待验收</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>产生可演示原型 ≥15 个</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>待验收</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>意向入孵/场景合作 ≥5 项</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>待验收</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>青年人才线索入库 ≥80 人</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>待验收</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>场地</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>岛上老厂房创客空间 / 实训平台周边（与主会场分流）</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>会务保障组</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>待锁定</t>
-        </is>
-      </c>
+          <t>持壁画 IP 授权的国企发起；寻求落户与政策支持；拟约 2000㎡、净高 9–11m 空间作产品/剧目基地；活动期可作沉浸体验打样。</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -6190,145 +7504,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>嘉宾分层与邀约目标</t>
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>择日专章｜9/15 前最靠近收官节点的黄道吉日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>主推9/12；备选9/9；规避9/10杨公忌日；黑客松绑定周五晚开营</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>层级</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>邀约对象</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>目标</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>负责人</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>确认状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>宜/要点</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>决策建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>A 政要领导层</t>
+          <t>首选</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>杨浦区委书记、区长（主致辞 / 揭牌）；分管副区长（科创 / 商务 / 建设 / 规划资源）；视情邀请市级相关部门（规划资源、科委、商务、外办）领导出席或书面致辞</t>
+          <t>2026 年 9 月 12 日（星期六 · 农历八月初二）</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>抬升政治规格，形成区级主场答卷画面</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
+          <t>开市·挂匾·立券·交易·出行</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>主推，服务9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>B 国际领事层</t>
+          <t>黑客松窗口</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>「一带一路」重点国家驻沪总领事 6–10 位亲自出席；领团代表或总领事俱乐部相关协调机制支持邀约；国别推介与国际会议厅冠名国对应总领事优先出席揭牌</t>
+          <t>2026 年 9 月 11 日（五）晚 — 9 月 12 日（六）下午（约 24 小时）</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>全球化规格与国际合作落位的核心背书</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
+          <t>创客夜→答卷日</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>与主会绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>C 产业·学术·创客层</t>
+          <t>备选一</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>具身智能 / 机器人 / AI 大模型 / 低空经济领军企业；量子城市 / 空间智能实验室与高校创新联盟代表；入岛孵化器、基金；黑客松导师与优胜团队代表</t>
+          <t>2026 年 9 月 9 日（星期三 · 农历七月廿八）</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>内容专业度、项目签约与创客生态可见度</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="52" customHeight="1">
+          <t>开市·交易·立券·出行</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>工作日备选</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>D 媒体与传播层</t>
+          <t>备选二</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>市级主流媒体、区融媒体中心；科技垂类与国际传播渠道；文脉短片、直播与短视频团队</t>
+          <t>2026 年 9 月 3 日（星期四 · 农历七月廿二）</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>领导可见、社会可感、国际可传</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>待启动</t>
+          <t>金匮黄道日</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>预热/路演</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>规避</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>杨公忌日</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>不安排主会</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/deliverables/复兴岛_全球创客岛_科创出海与具身智能国际大会_执行计划表.xlsx
+++ b/deliverables/复兴岛_全球创客岛_科创出海与具身智能国际大会_执行计划表.xlsx
@@ -15,21 +15,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.规划与课题" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.敦煌项目" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.冷启动角色" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.择日专章" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.详细议程" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.体验游戏层" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.黑客松专章" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.嘉宾邀请" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.一带一路国别池" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14.揭牌落位" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15.席位结构" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16.组织架构" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17.倒排期" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18.预算测算" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19.KPI成效" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20.风险预案" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21.下一步行动" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22.主题板块" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.杨浦企业互动" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.择日专章" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.详细议程" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.体验游戏层" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.黑客松专章" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.嘉宾邀请" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14.一带一路国别池" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15.揭牌落位" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16.席位结构" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17.组织架构" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18.倒排期" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19.预算测算" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20.KPI成效" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21.风险预案" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22.下一步行动" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23.主题板块" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1.活动总览'!$1:$4</definedName>
@@ -39,21 +40,22 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'5.规划与课题'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'6.敦煌项目'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'7.冷启动角色'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'8.择日专章'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'9.详细议程'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'10.体验游戏层'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'11.黑客松专章'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'12.嘉宾邀请'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'13.一带一路国别池'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'14.揭牌落位'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'15.席位结构'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'16.组织架构'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'17.倒排期'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="18">'18.预算测算'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">'19.KPI成效'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">'20.风险预案'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="21">'21.下一步行动'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="22">'22.主题板块'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'8.杨浦企业互动'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'9.择日专章'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'10.详细议程'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'11.体验游戏层'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'12.黑客松专章'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'13.嘉宾邀请'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'14.一带一路国别池'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'15.揭牌落位'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'16.席位结构'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'17.组织架构'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'18.倒排期'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'19.预算测算'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">'20.KPI成效'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">'21.风险预案'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="22">'22.下一步行动'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="23">'23.主题板块'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -604,14 +606,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2026 复兴岛·全球创客岛收官答卷大会｜Excel 执行呈现台账（V3）</t>
+          <t>创客复兴·智汇杨浦｜上海复兴岛「全球创客岛」阶段性成果发布暨科创出海与具身智能国际峰会</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>V3.0 · 建议稿｜主论坛+分论坛+体验层+黑客松｜敦煌意向｜主会日 2026-09-12</t>
+          <t>V3.1 · 建议稿｜杨浦AI企业互动｜四层结构｜敦煌意向｜主会日 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1006,17 +1008,17 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>8.择日专章</t>
+          <t>8.杨浦企业互动</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>首选/备选/规避</t>
+          <t>优刻得/智谱/苏度等</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>日期决策</t>
+          <t>企业邀约</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1028,17 +1030,17 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>9.详细议程</t>
+          <t>9.择日专章</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>全天含分论坛D与体验层</t>
+          <t>首选/备选/规避</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>现场脚本</t>
+          <t>日期决策</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1050,17 +1052,17 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>10.体验游戏层</t>
+          <t>10.详细议程</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>五关卡集章任务</t>
+          <t>含杨浦AI力量环节</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>体验执行</t>
+          <t>现场脚本</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1072,17 +1074,17 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>11.黑客松专章</t>
+          <t>11.体验游戏层</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>赛道/赛程/规则/KPI</t>
+          <t>五关卡集章任务</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>创客执行</t>
+          <t>体验执行</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1094,17 +1096,17 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>12.嘉宾邀请</t>
+          <t>12.黑客松专章</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>政要/领事/产业/创客</t>
+          <t>赛道/赛程/规则/KPI</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>邀约台账</t>
+          <t>创客执行</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1116,17 +1118,17 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>13.一带一路国别池</t>
+          <t>13.嘉宾邀请</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>拟邀国家</t>
+          <t>政要/领事/杨浦企业</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>国际资源</t>
+          <t>邀约台账</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1138,17 +1140,17 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>14.揭牌落位</t>
+          <t>14.一带一路国别池</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>会客厅+敦煌意向</t>
+          <t>拟邀国家</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>硬成果</t>
+          <t>国际资源</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -1160,17 +1162,17 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>15.席位结构</t>
+          <t>15.揭牌落位</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>主会席别</t>
+          <t>会客厅+敦煌意向</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>会务排座</t>
+          <t>硬成果</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1182,17 +1184,17 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>16.组织架构</t>
+          <t>16.席位结构</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>含智库/文旅/黑客松</t>
+          <t>主会席别</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>分工责任</t>
+          <t>会务排座</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1204,17 +1206,17 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>17.倒排期</t>
+          <t>17.组织架构</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>节点任务</t>
+          <t>含智库/文旅/黑客松</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>进度表</t>
+          <t>分工责任</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1226,17 +1228,17 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>18.预算测算</t>
+          <t>18.倒排期</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>分项费用</t>
+          <t>节点任务</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>资金安排</t>
+          <t>进度表</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -1248,17 +1250,17 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>19.KPI成效</t>
+          <t>19.预算测算</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>验收标准</t>
+          <t>分项费用</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>复盘</t>
+          <t>资金安排</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1270,17 +1272,17 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>20.风险预案</t>
+          <t>20.KPI成效</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>风险对策</t>
+          <t>验收标准</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>应急</t>
+          <t>复盘</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -1292,20 +1294,42 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>21.下一步行动</t>
+          <t>21.风险预案</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>含敦煌48h核查</t>
+          <t>风险对策</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
+          <t>应急</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>22.下一步行动</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>企业锁定+敦煌核查</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
           <t>立即执行</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1337,7 +1361,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>择日专章｜9/15 前最靠近收官节点的黄道吉日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>主推9/12；备选9/9；规避9/10杨公忌日；黑客松绑定周五晚开营</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>宜/要点</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>决策建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>首选</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>2026 年 9 月 12 日（星期六 · 农历八月初二）</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>开市·挂匾·立券·交易·出行</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>主推，服务9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>黑客松窗口</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>2026 年 9 月 11 日（五）晚 — 9 月 12 日（六）下午（约 24 小时）</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>创客夜→答卷日</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>与主会绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>备选一</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>2026 年 9 月 9 日（星期三 · 农历七月廿八）</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>开市·交易·立券·出行</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>工作日备选</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>备选二</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>2026 年 9 月 3 日（星期四 · 农历七月廿二）</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>金匮黄道日</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>预热/路演</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>规避</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>杨公忌日</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>不安排主会</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1358,7 +1553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>主论坛+四分论坛+体验层+黑客松Demo Day</t>
+          <t>含「杨浦AI力量」企业环节 + 四分论坛 + 体验层 + Demo Day</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1789,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10:10–10:35</t>
+          <t>10:10–10:30</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1626,22 +1821,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>10:35–11:05</t>
+          <t>10:30–10:55</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>国际会议厅/会客厅揭牌</t>
+          <t>杨浦AI力量 · 企业高端发言</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>国家厅+片区厅揭牌、铭牌落位、文脉场景合影</t>
+          <t>优刻得/智谱/苏度等 2–3 家各 5–8 分钟</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>区领导+领事</t>
+          <t>科企联+企业</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1658,22 +1853,22 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>11:05–11:35</t>
+          <t>10:55–11:20</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>重点项目签约/意向</t>
+          <t>国际会议厅/会客厅揭牌</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>入岛企业、出海合作；敦煌等一事一议（视成熟度）</t>
+          <t>国家厅+片区厅揭牌、铭牌落位、文脉场景合影</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>区商务/科委</t>
+          <t>区领导+领事</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1690,22 +1885,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>11:35–12:00</t>
+          <t>11:20–11:45</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>集体合影 · 媒体发布</t>
+          <t>重点项目签约/意向</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>领导—领事—企业—创客代表同框</t>
+          <t>杨浦企业互动签约；敦煌等一事一议（视成熟度）</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>宣传组</t>
+          <t>区商务/科委</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1722,22 +1917,22 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>12:00–13:30</t>
+          <t>11:45–12:05</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>工作午宴/闭门交流（可选）</t>
+          <t>集体合影 · 媒体发布</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>小范围深度沟通；黑客松初审；体验层轮转</t>
+          <t>领导—领事—杨浦企业—创客代表同框</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>外事+黑客松</t>
+          <t>宣传组</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1749,27 +1944,27 @@
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>下午</t>
+          <t>上午</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>13:30–15:00</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>分论坛 A：文脉·空间·量子城市</t>
+          <t>工作午宴/闭门交流（可选）</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>治江治城、遗存活化、空间智能课题</t>
+          <t>小范围深度沟通；黑客松初审；体验层轮转</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>规划/科委</t>
+          <t>外事+黑客松</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1791,17 +1986,17 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>分论坛 B：具身智能与低空经济</t>
+          <t>分论坛 A：文脉·空间·量子城市</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>实训平台、场景合作、产业链对接</t>
+          <t>治江治城、遗存活化、空间智能课题</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>产业专班</t>
+          <t>规划/科委</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1823,17 +2018,17 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>分论坛 C：科创出海圆桌</t>
+          <t>分论坛 B：具身智能与低空经济</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>分国别对接桌：领事×出海企业</t>
+          <t>实训平台、场景合作、产业链对接</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>商务/外事</t>
+          <t>产业专班</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1855,17 +2050,17 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>分论坛 D：敦煌·文旅科技沉浸</t>
+          <t>分论坛 C：科创出海圆桌</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>IP/空间/机器人互动/商业模型；一事一议路径</t>
+          <t>分国别对接桌：领事×出海企业</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>文旅+科企联</t>
+          <t>商务/外事</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1887,17 +2082,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>体验层/黑客松观摩</t>
+          <t>分论坛 D：敦煌·文旅科技沉浸</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>沉浸关卡限流体验；黑客松工位开放（限流）</t>
+          <t>IP/空间/机器人互动/商业模型；一事一议路径</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>体验+黑客松</t>
+          <t>文旅+科企联</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1914,22 +2109,22 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>15:00–15:20</t>
+          <t>13:30–15:00</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>茶歇 · 展示体验</t>
+          <t>体验层/黑客松观摩</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>具身演示、低空静态展、敦煌样片/短时体验</t>
+          <t>沉浸关卡限流体验；黑客松工位开放（限流）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>展示组</t>
+          <t>体验+黑客松</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1946,22 +2141,22 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>15:20–16:20</t>
+          <t>15:00–15:20</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Demo Day · 高端对话</t>
+          <t>茶歇 · 展示体验</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>黑客松决赛路演 + 「论坛×游戏化体验」复盘对话</t>
+          <t>具身演示、低空静态展、敦煌样片/短时体验</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>主持+评委</t>
+          <t>展示组</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1978,22 +2173,22 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>16:20–16:50</t>
+          <t>15:20–16:20</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>颁奖与下一阶段行动</t>
+          <t>Demo Day · 高端对话</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>黑客松颁奖；百日行动/会客厅/敦煌跟进清单</t>
+          <t>黑客松决赛路演 + 「论坛×游戏化体验」复盘对话</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>专班</t>
+          <t>主持+评委</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2010,25 +2205,57 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
+          <t>16:20–16:50</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>颁奖与下一阶段行动</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>黑客松颁奖；百日行动/会客厅/敦煌跟进清单</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>专班</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
           <t>16:50–17:30</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>国际对接酒会</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>领事—企业—优胜创客—文旅方自由对接</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>会务组</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
@@ -2044,7 +2271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2069,7 +2296,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>非电竞：沉浸关卡+集章任务；与分论坛D（敦煌）、黑客松互相导流</t>
+          <t>非电竞：沉浸关卡+集章任务；苏度/卓益得等真机互动+敦煌关卡</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2401,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>文脉展示组</t>
+          <t>产业内容组</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2237,7 +2464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2848,7 +3075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2857,8 +3084,8 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -2867,7 +3094,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>嘉宾分层与邀约目标</t>
+          <t>嘉宾分层与邀约目标（含杨浦企业主力军）</t>
         </is>
       </c>
     </row>
@@ -2947,17 +3174,17 @@
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>C 产业·学术·创客层</t>
+          <t>C 杨浦产业主力军（重点互动）</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>具身智能 / 机器人 / AI 大模型 / 低空经济领军企业；量子城市 / 空间智能实验室与高校创新联盟代表；入岛孵化器、基金；黑客松导师与优胜团队代表</t>
+          <t>优刻得、智谱 AI（算力与大模型）；苏度科技、卓益得、傲鲨智能、清宝引擎（具身智能）；声网、道客、商米等杨浦数字经济优质企业；黑客松导师与优胜团队</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>内容专业度、项目签约与创客生态可见度</t>
+          <t>区内存量企业上岛互动，形成「杨浦 AI 回家乡」画面</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
@@ -2999,7 +3226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3324,7 +3551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3548,7 +3775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3755,7 +3982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3976,7 +4203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4328,424 +4555,6 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>预算测算（示意，单位：万元）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>金额单位：人民币万元，仅供测算示意。可通过国资载体场地置换、企业赞助、会客厅共建方分摊、政策券包兑现等方式降低区级现金支出。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>成本项</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>预算低值</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>预算高值</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>中值参考</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>场地租赁与基础改造/布置</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>主会场+展廊+船台礼仪动线；国企/区属载体可置换</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>黑客松场地与通宵保障</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>工位、网络、值守、夜宵、安全</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>舞台视听与同声传译</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>多语同传、大屏、直播机位</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>外事礼宾与接待</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>领事用车、休息室、伴手礼、翻译</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>揭牌空间与铭牌制作</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>首批会客厅基础形象与铭牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>文脉短片与展陈</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>影像、展板、互动装置</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>黑客松奖金与券包激励</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>奖金+算力/模型券对接；可与政策券包联动</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>物料视觉与印刷</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>主视觉、手册、胸卡、导视</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>餐饮茶歇与轻酒会</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>主会 200–300 人；不做大型晚宴</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>媒体传播与直播剪辑</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>通稿、短视频、摄影摄像</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>安保交通医疗应急</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>大型涉外+通宵活动标准</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>执行团队与不可预见费</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>含机动 10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>合计（示意）</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>中值约 70 万；场地/券包置换后现金可压至约 50 万</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4771,7 +4580,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>2026 复兴岛·全球创客岛收官答卷大会｜活动总览</t>
+          <t>创客复兴·智汇杨浦｜活动总览</t>
         </is>
       </c>
     </row>
@@ -4807,88 +4616,88 @@
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>活动名称</t>
+          <t>活动主题</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026 复兴岛·全球创客岛收官答卷大会</t>
+          <t>创客复兴·智汇杨浦</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>副标题</t>
+          <t>活动全称</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>科创出海 × 人工智能 × 具身智能国际大会</t>
+          <t>上海复兴岛「全球创客岛」阶段性成果发布暨科创出海与具身智能国际峰会</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>主题Slogan</t>
+          <t>主题定位</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>百年复兴，智造再启航</t>
+          <t>人工智能赋能 · 具身智能落地 · 国际合作揭牌 · 创客生态启航</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>建议时间</t>
+          <t>Slogan</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>2026 年 9 月 12 日（星期六 · 农历八月初二）（主会日）；黑客松 2026 年 9 月 11 日（五）晚 — 9 月 12 日（六）下午（约 24 小时）</t>
+          <t>锚定全球创客岛，答卷量子城市</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>建议时间</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>2026 年 9 月 12 日（星期六 · 农历八月初二）（主会日）；黑客松 2026 年 9 月 11 日（五）晚 — 9 月 12 日（六）下午（约 24 小时）</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
           <t>黄历择吉</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>宜开市 · 挂匾 · 立券 · 出行 · 交易（详见择日专章）</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>建议地点</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>复兴岛核心启动区 / 船台公园及周边高净高工业厂房</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>建议地点</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>复兴岛核心启动区 / 船台公园及周边高净高工业厂房</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
           <t>活动规模</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>主会场 200–300 人；黑客松 20–40 队；体验层另计流动人次</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>核心主题</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>文脉续写 · 科创出海 · AI/具身/低空 · 敦煌文旅科技 · 黑客松</t>
         </is>
       </c>
     </row>
@@ -4905,34 +4714,34 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>规格目标</t>
+          <t>杨浦企业互动</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>区委书记/区长出席；一带一路总领事；敦煌等一事一议样本</t>
+          <t>优刻得、智谱、苏度、卓益得、傲鲨等算力/模型/具身企业同台</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>规格目标</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>区委书记/区长出席；一带一路总领事；敦煌等一事一议样本</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
           <t>关键成果</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>成果发布 + 会客厅揭牌 + 项目意向/签约 + Demo Day + 沉浸体验打样</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>协同机制</t>
-        </is>
-      </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>创客学院/云基地智库顾问 + 科企联活动招商转化</t>
+          <t>成果发布 + 会客厅揭牌 + 企业互动签约 + Demo Day + 沉浸体验打样</t>
         </is>
       </c>
     </row>
@@ -4952,6 +4761,424 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>预算测算（示意，单位：万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>金额单位：人民币万元，仅供测算示意。可通过国资载体场地置换、企业赞助、会客厅共建方分摊、政策券包兑现等方式降低区级现金支出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>成本项</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>预算低值</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>预算高值</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>中值参考</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>场地租赁与基础改造/布置</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>主会场+展廊+船台礼仪动线；国企/区属载体可置换</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>黑客松场地与通宵保障</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>工位、网络、值守、夜宵、安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>舞台视听与同声传译</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>多语同传、大屏、直播机位</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>外事礼宾与接待</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>领事用车、休息室、伴手礼、翻译</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>揭牌空间与铭牌制作</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>首批会客厅基础形象与铭牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>文脉短片与展陈</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>影像、展板、互动装置</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>黑客松奖金与券包激励</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>奖金+算力/模型券对接；可与政策券包联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>物料视觉与印刷</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>主视觉、手册、胸卡、导视</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>餐饮茶歇与轻酒会</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>主会 200–300 人；不做大型晚宴</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>媒体传播与直播剪辑</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>通稿、短视频、摄影摄像</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>安保交通医疗应急</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>大型涉外+通宵活动标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>执行团队与不可预见费</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>含机动 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>合计（示意）</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>中值约 70 万；场地/券包置换后现金可压至约 50 万</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5153,7 +5380,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5350,13 +5577,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5368,7 +5595,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>下一步行动清单（含敦煌 48h 核查）</t>
+          <t>下一步行动清单（主题定稿 · 企业锁定 · 敦煌核查）</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5627,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>本周内：确认「9/12 主日期 + 9/9 备选」与四层结构命名（含黑客松、体验层）。</t>
+          <t>本周内：确认主题「创客复兴·智汇杨浦」与主会日 9/12（备选 9/9）。</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -5420,12 +5647,12 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>对接会后 48 小时：输出敦煌事实核查表（950 万口径、空间、政策诉求、机器人能力）。</t>
+          <t>锁定优刻得、智谱、苏度等企业主论坛/分论坛/体验层互动名单</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>对接会后48小时</t>
+          <t>本周内</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -5440,12 +5667,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>3 日内：踏勘候选 2000㎡ / 净高 9–11m 厂房，评估 9 月可呈现度（体验打样 or 仅路演）。</t>
+          <t>本周内：锁定优刻得、智谱、苏度、卓益得等企业互动名单（主论坛发言/分论坛/体验层/黑客松导师）。</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>3日内</t>
+          <t>对接会后48小时</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -5460,12 +5687,12 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>1 周内：成立专班（智库顾问组、生态转化组、文旅沉浸组、黑客松组），明确组长。</t>
+          <t>对接会后 48 小时：输出敦煌事实核查表（950 万口径、空间、政策诉求、机器人能力）。</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>1周内</t>
+          <t>3日内</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -5480,7 +5707,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>1 周内：锁定主会场、体验层/黑客松厂房与首批 3 个揭牌对象谈判文本。</t>
+          <t>3 日内：踏勘候选 2000㎡ / 净高 9–11m 厂房，评估 9 月可呈现度（体验打样 or 仅路演）。</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5500,12 +5727,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>10 日内：总领事邀约 + 黑客松报名上线 + 外事报批；敦煌达线则启动一事一议报区。</t>
+          <t>1 周内：成立专班（智库顾问组、生态转化组、文旅沉浸组、黑客松组），明确组长。</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>10日内</t>
+          <t>1周内</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -5520,15 +5747,55 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
+          <t>1 周内：锁定主会场、体验层/黑客松厂房与首批 3 个揭牌对象谈判文本。</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>10日内</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>10 日内：总领事邀约 + 黑客松报名上线 + 外事报批；敦煌达线则启动一事一议报区。</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>同步推进</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
           <t>同步：完成主视觉与「一页纸」请示件（附 PPT+Excel），供区主要领导决策。</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>同步推进</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>待启动</t>
         </is>
@@ -5543,7 +5810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7504,165 +7771,450 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>择日专章｜9/15 前最靠近收官节点的黄道吉日</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>杨浦 AI / 具身智能优质企业互动清单</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>主推9/12；备选9/9；规避9/10杨公忌日；黑客松绑定周五晚开营</t>
+          <t>优刻得·智谱·苏度·卓益得等上岛同台｜主论坛发言+分论坛+体验层+黑客松导师</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>宜/要点</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>决策建议</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>赛道</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>杨浦关联</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>活动互动角色</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>邀约状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>首选</t>
+          <t>优刻得 UCloud</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026 年 9 月 12 日（星期六 · 农历八月初二）</t>
+          <t>智算/云计算</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>开市·挂匾·立券·交易·出行</t>
+          <t>杨浦科创板云企；智算中心与大模型底座</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>主推，服务9/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>主论坛技术底座发言；黑客松算力/云资源赞助；分论坛 B 或算力圆桌</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>待邀约</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>黑客松窗口</t>
+          <t>智谱 AI</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026 年 9 月 11 日（五）晚 — 9 月 12 日（六）下午（约 24 小时）</t>
+          <t>大模型</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>创客夜→答卷日</t>
+          <t>与优刻得共建超千卡推理集群等生态合作</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>与主会绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>主论坛/分论坛模型应用分享；黑客松模型 API/导师支持</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>待邀约</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>备选一</t>
+          <t>苏度科技</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>2026 年 9 月 9 日（星期三 · 农历七月廿八）</t>
+          <t>具身智能</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>开市·交易·立券·出行</t>
+          <t>杨浦重点具身智能企业；WAIC 相关签约与技术突破</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>工作日备选</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>具身分论坛核心路演；体验层真机互动；实训场景合作意向</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>待邀约</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>备选二</t>
+          <t>卓益得机器人</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026 年 9 月 3 日（星期四 · 农历七月廿二）</t>
+          <t>人形/具身</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>金匮黄道日</t>
+          <t>上理成果转化；杨数浦/WAIC 杨浦团代表企业</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>预热/路演</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>体验层人形互动；分论坛 B 案例；硅基岛民/巡游展示</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>待邀约</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>规避</t>
+          <t>傲鲨智能</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>外骨骼</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>杨公忌日</t>
+          <t>杨浦专精特新；大学路/WAIC 杨浦团常客</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>不安排主会</t>
+          <t>体验层可穿戴互动；产业分论坛场景分享</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>待邀约</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>清宝引擎</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>仿生人形</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>杨浦具身智能创新企业</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>体验层/展示区真机；黑客松具身赛道导师候选</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>待邀约</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>声网 Agora</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>实时互动 AI</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>大创智孵化培育代表企业</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>同传/直播技术支持或分论坛实时互动方案</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>待邀约</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>道客网络 DaoCloud</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>云原生/算力调度</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>杨数浦 WAIC 参展企业</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>算力调度/云原生圆桌；黑客松基础设施支持</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>待邀约</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>商米科技</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>物理 AI/智能终端</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>大学路物理 AI 样板商业落地</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>体验层商业场景打样；AI+消费对话</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>待邀约</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>美团无人机（场景方）</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>低空经济</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>杨浦低空物流试点与杨数浦展示</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>低空分论坛/静态展；与岛上测试叙事衔接</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>待邀约</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>互动机制</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>责任方</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>主论坛「杨浦AI力量」环节</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>优刻得+智谱等 2–3 家作 5–8 分钟高端发言，体现区内存量优质企业</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>科企联+产业内容组</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>分论坛 B 企业对话</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>苏度、卓益得、傲鲨等具身企业圆桌：从实验室到岛上实景</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>科企联+产业内容组</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>体验层企业工位</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>真机互动、外骨骼试穿、算力/模型演示，形成可传播画面</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>科企联+产业内容组</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>黑客松产业导师</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>优刻得算力、智谱模型、具身企业导师坐镇，优胜可获入孵/联调资源</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>科企联+产业内容组</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>签约/意向墙</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>企业与岛上场景、敦煌文旅、出海通道的合作意向集中呈现</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>科企联+产业内容组</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>媒体点名</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>通稿与短视频突出「杨浦企业回家乡岛上办会、与全球创客同框」</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>科企联+产业内容组</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/deliverables/复兴岛_全球创客岛_科创出海与具身智能国际大会_执行计划表.xlsx
+++ b/deliverables/复兴岛_全球创客岛_科创出海与具身智能国际大会_执行计划表.xlsx
@@ -21,16 +21,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.体验游戏层" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.黑客松专章" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.嘉宾邀请" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14.一带一路国别池" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15.揭牌落位" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16.席位结构" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17.组织架构" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18.倒排期" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19.预算测算" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20.KPI成效" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21.风险预案" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22.下一步行动" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23.主题板块" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14.东亚东南亚领事" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15.一带一路国别池" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16.揭牌落位" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17.席位结构" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18.组织架构" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19.倒排期" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20.预算测算" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21.KPI成效" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22.风险预案" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23.下一步行动" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24.主题板块" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1.活动总览'!$1:$4</definedName>
@@ -46,16 +47,17 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'11.体验游戏层'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'12.黑客松专章'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'13.嘉宾邀请'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'14.一带一路国别池'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'15.揭牌落位'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'16.席位结构'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'17.组织架构'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="18">'18.倒排期'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">'19.预算测算'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">'20.KPI成效'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="21">'21.风险预案'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="22">'22.下一步行动'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="23">'23.主题板块'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'14.东亚东南亚领事'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'15.一带一路国别池'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'16.揭牌落位'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'17.席位结构'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'18.组织架构'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'19.倒排期'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">'20.预算测算'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">'21.KPI成效'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="22">'22.风险预案'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="23">'23.下一步行动'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="24">'24.主题板块'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -157,7 +159,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -179,11 +181,80 @@
         <color rgb="00D5DEEB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D5DEEB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D5DEEB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5DEEB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5DEEB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5DEEB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D5DEEB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D5DEEB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D5DEEB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5DEEB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D5DEEB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -208,9 +279,14 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -613,7 +689,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>V3.1 · 建议稿｜杨浦AI企业互动｜四层结构｜敦煌意向｜主会日 2026-09-12</t>
+          <t>V3.2 · 建议稿｜杨浦AI企业互动｜四层结构｜敦煌意向｜主会日 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -764,17 +840,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>总领事≥6国</t>
+          <t>东亚+东南亚11国</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>一带一路亲自出席</t>
+          <t>按全部出席准备；底线≥6国</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>见嘉宾邀请</t>
+          <t>见领事名单</t>
         </is>
       </c>
     </row>
@@ -1140,17 +1216,17 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>14.一带一路国别池</t>
+          <t>14.东亚东南亚领事</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>拟邀国家</t>
+          <t>11国总领事姓名+安排</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>国际资源</t>
+          <t>外事邀约主台账</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -1162,17 +1238,17 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>15.揭牌落位</t>
+          <t>15.一带一路国别池</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>会客厅+敦煌意向</t>
+          <t>延伸拟邀国家</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>硬成果</t>
+          <t>国际资源</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1184,17 +1260,17 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>16.席位结构</t>
+          <t>16.揭牌落位</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>主会席别</t>
+          <t>会客厅+敦煌意向</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>会务排座</t>
+          <t>硬成果</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1206,17 +1282,17 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>17.组织架构</t>
+          <t>17.席位结构</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>含智库/文旅/黑客松</t>
+          <t>主会席别</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>分工责任</t>
+          <t>会务排座</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1228,17 +1304,17 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>18.倒排期</t>
+          <t>18.组织架构</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>节点任务</t>
+          <t>含智库/文旅/黑客松</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>进度表</t>
+          <t>分工责任</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -1250,17 +1326,17 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>19.预算测算</t>
+          <t>19.倒排期</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>分项费用</t>
+          <t>节点任务</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>资金安排</t>
+          <t>进度表</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1272,17 +1348,17 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>20.KPI成效</t>
+          <t>20.预算测算</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>验收标准</t>
+          <t>分项费用</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>复盘</t>
+          <t>资金安排</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -1294,17 +1370,17 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>21.风险预案</t>
+          <t>21.KPI成效</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>风险对策</t>
+          <t>验收标准</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>应急</t>
+          <t>复盘</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1316,17 +1392,17 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>22.下一步行动</t>
+          <t>22.风险预案</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>企业锁定+敦煌核查</t>
+          <t>风险对策</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>立即执行</t>
+          <t>应急</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -1341,8 +1417,16 @@
           <t>以百年「复兴」文脉与「敦煌」级文化 IP 为双引擎，以 9 月 15 日前收官节点为政治死线，在岛上以「主论坛 + 分论坛 + 沉浸式体验/游戏层 + 黑客松」组合拳，完成成果发布、国际会客厅揭牌与高价值项目（含敦煌意向）一事一议展示，形成可汇报、可传播、可复用的冷启动答卷。</t>
         </is>
       </c>
-    </row>
-    <row r="40"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="12" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="14" t="n"/>
+      <c r="D40" s="15" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
@@ -1371,7 +1455,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>择日专章｜9/15 前最靠近收官节点的黄道吉日</t>
         </is>
@@ -1385,22 +1469,22 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>宜/要点</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>决策建议</t>
         </is>
@@ -1544,7 +1628,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>详细议程｜2026 年 9 月 12 日（星期六 · 农历八月初二）</t>
         </is>
@@ -1762,12 +1846,12 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>「一带一路」领事代表致辞</t>
+          <t>东亚/东南亚领事代表致辞</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>国际合作与科技出海期待</t>
+          <t>邻域合作与科技出海期待（可轮值 1–2 位）</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -2287,7 +2371,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>体验 / 游戏层关卡设计（论坛×游戏化体验）</t>
         </is>
@@ -2480,7 +2564,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>「船台·智能体」复兴创客黑客松｜执行台账</t>
         </is>
@@ -2494,22 +2578,22 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -3092,7 +3176,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>嘉宾分层与邀约目标（含杨浦企业主力军）</t>
         </is>
@@ -3151,17 +3235,17 @@
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>B 国际领事层</t>
+          <t>B 国际领事层（东亚+东南亚优先）</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>「一带一路」重点国家驻沪总领事 6–10 位亲自出席；领团代表或总领事俱乐部相关协调机制支持邀约；国别推介与国际会议厅冠名国对应总领事优先出席揭牌</t>
+          <t>暂按东亚+东南亚驻沪总领事全部出席准备（约 11 国，见领事名单）；揭牌国对应总领事优先本人出席；其余国安排致辞/圆桌/酒会对接；经区外办规范邀约；可借助总领事俱乐部等协调机制并联推进</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>全球化规格与国际合作落位的核心背书</t>
+          <t>全球化规格与国际合作落位的核心背书；形成「邻域全覆盖」画面</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
@@ -3227,6 +3311,579 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>东亚 + 东南亚驻沪总领事名单（暂按全部出席准备）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>以上名单据各驻沪总领事馆官网、外交部公开信息及近期外事报道整理（截至 2026-07），用于会务席位、礼宾与邀约台账准备；正式称谓、性别敬称与是否本人出席，一律以区外办/市外办报批确认及各馆书面回复为准。策划阶段暂按「全部参加」预留席位与接待资源。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>策划口径：席位/用车/伴手礼/同传按 11 国全员预留；正式出席以外事书面确认为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>片区</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>国家</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>总领事（中文）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>英文名</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>合作侧重</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>现场安排</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>确认状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>东亚</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>冈田胜</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Okada Masaru</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>制造、机器人、低碳与产业技术合作</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>拟邀本人出席；揭牌/主论坛优先候选</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>按全部出席准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>东亚</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>韩国</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>金英俊</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Young-jun Kim</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>半导体、消费电子、跨境电商与文创</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>拟邀本人出席；出海/产业圆桌</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>按全部出席准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>东亚</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>蒙古国</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>道尔吉德日木·宝勒德</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Dorjderem Bold</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>资源能源、跨境通道与教育人文</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>拟邀本人出席；国际对接酒会</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>按全部出席准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>东南亚</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>陈子勤</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Tan Chee King</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>总部经济、金融与数字贸易枢纽</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>拟邀本人出席；揭牌/主论坛优先候选</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>按全部出席准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>东南亚</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>马来西亚</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>沙哈菲兹·沙哈里斯</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Mohd Shahafeez Shaharis</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>电子制造、数据中心、清真经济</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>拟邀本人出席；分论坛 C 出海对接</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>按全部出席准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>东南亚</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>陈佩恩</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Tachaphorn Suntrajarn</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>智能制造、新能源配套、消费市场</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>拟邀本人出席；揭牌候选 / 国别推介</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>按全部出席准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>东南亚</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>印度尼西亚</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>邯伯盼</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Berlianto Situngkir</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>数字经济、资源与消费市场</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>拟邀本人出席；出海圆桌与酒会</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>按全部出席准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>东南亚</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>陈辉雄</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Tran Huy Hung</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>电子制造转移、供应链协同</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>拟邀本人出席；分论坛 C 对接桌</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>按全部出席准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>东南亚</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>菲律宾</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>方明易</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Myca Fischer</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>BPO、数字服务、基建与消费</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>拟邀本人出席；国际对接酒会</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>按全部出席准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>东南亚</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>宁维斯</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Nguon Visoth</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>产能合作、基建与农业加工</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>拟邀本人出席；国别推介 / 酒会</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>按全部出席准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>东南亚</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>老挝</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>维达万·桥本控</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Vidavone Keobounkhong</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>中老铁路沿线经贸与人文交流</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>拟邀本人出席；国际对接酒会</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>按全部出席准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>暂未在沪设总领事馆（不纳入本场全员预留，一事一议）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>· 缅甸：目前未在上海设总领事馆；领事事务多由驻华使馆或驻昆明/南宁/重庆总领馆等办理</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>· 文莱：目前未在上海设总领事馆；对华事务由驻华大使馆统筹</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>· 朝鲜：驻沪总领事馆已于历史上闭馆；现有驻华机构主要为驻华使馆及驻沈阳总领馆等</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>· 东帝汶：目前未见驻沪总领事馆公开信息；涉及合作可一事一议协调使馆层面</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A22:H22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3244,9 +3901,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>拟邀「一带一路」国家参考池</t>
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>拟邀「一带一路」延伸国家参考池（中东/中亚/中东欧）</t>
         </is>
       </c>
     </row>
@@ -3298,15 +3955,19 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>待定</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>待邀约</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr"/>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>东亚东南亚见上一表</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="7" t="n">
@@ -3324,15 +3985,19 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>待定</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>待邀约</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr"/>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>东亚东南亚见上一表</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -3350,15 +4015,19 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>待定</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>待邀约</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>东亚东南亚见上一表</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="7" t="n">
@@ -3381,10 +4050,14 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>待邀约</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr"/>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>东亚东南亚见上一表</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="5" t="n">
@@ -3407,10 +4080,14 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>待邀约</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr"/>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>东亚东南亚见上一表</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -3433,10 +4110,14 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>待邀约</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr"/>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>东亚东南亚见上一表</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="5" t="n">
@@ -3459,10 +4140,14 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>待邀约</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr"/>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>东亚东南亚见上一表</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -3485,10 +4170,14 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>待邀约</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr"/>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>东亚东南亚见上一表</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="5" t="n">
@@ -3511,10 +4200,14 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>待邀约</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr"/>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>东亚东南亚见上一表</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -3537,10 +4230,14 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>待邀约</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr"/>
+          <t>待评估</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>东亚东南亚见上一表</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3551,7 +4248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3569,7 +4266,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>国际会议厅 / 会客厅揭牌落位计划（含敦煌视进度）</t>
         </is>
@@ -3720,42 +4417,42 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>落位原则</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>· 先锁意向、再上仪式：揭牌对象须在活动前完成协议文本与空间确认。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>· 一国一厅、一厅一责：明确运营主体、年度活动频次与招商指标。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>· 外事合规：领事出席与冠名事项提前报区外办 / 市外办指导。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>· 文脉同框：揭牌背景尽量融入船台/塔吊/老厂房元素，形成独特视觉记忆。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>· 媒体可感知：揭牌背板、铭牌、导视与文脉短片同步备妥。</t>
         </is>
@@ -3775,7 +4472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3791,7 +4488,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>席位结构（主会场 200–300 人）</t>
         </is>
@@ -3827,12 +4524,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>30–40</t>
+          <t>40–55</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>区领导、市级嘉宾、总领事、揭牌对象代表</t>
+          <t>区领导、市级嘉宾、东亚+东南亚总领事（按全员预留）、揭牌对象代表</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -3982,7 +4679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3998,7 +4695,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>组织架构与职责（含智库/文旅/黑客松）</t>
         </is>
@@ -4197,365 +4894,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>执行倒排期</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>节点</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>关键任务</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>责任组</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>T-50 天（7 月底前）</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>立项与专班成立；确定 9/12 主日期与 9/9 备选；启动外事报批窗口沟通</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>综合协调组</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>T-45 天</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>锁定主会场与黑客松厂房；形成揭牌候选短名单；启动文脉短片脚本</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>文旅沉浸组</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>T-40 天</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>正式外事报批；首轮总领事邀约；黑客松赛题与报名通道上线</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>外事礼宾组</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>T-30 天</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>确认至少 2 个国家厅+1 个片区厅意向；签约清单初稿；主视觉定稿</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>空间落位组</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>T-21 天</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>总领事出席确认过半；分论坛嘉宾锁定；黑客松报名截止与初筛</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>T-14 天</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>全要素彩排脚本；揭牌铭牌进场；开放数据/API 包发给入围队伍</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>产业内容组</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>T-7 天</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>最终座次；同传联调；黑客松夜间值守与安全预案桌面推演</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>会务保障组</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>T-2 天</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>会场与工位布置完成；领导/领事行程再确认；演示设备验收</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>宣传媒体组</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>9/11 晚</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>黑客松开营</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>黑客松组</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>活动日 9/12</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>主会场+Demo Day+揭牌签约按议程执行</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>综合协调组</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>T+3 天</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>新闻通稿与短视频；领导汇报材料（一页纸+图文册）提交</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>宣传媒体组</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>T+14 天</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>会客厅运营启动会；黑客松优胜转化台账；复盘报告</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>文旅沉浸组</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>待启动</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4578,7 +4916,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>创客复兴·智汇杨浦｜活动总览</t>
         </is>
@@ -4731,7 +5069,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>区委书记/区长出席；一带一路总领事；敦煌等一事一议样本</t>
+          <t>区委书记/区长出席；东亚+东南亚总领事全覆盖准备；敦煌等一事一议样本</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -4761,6 +5099,365 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>执行倒排期</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>关键任务</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>责任组</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>T-50 天（7 月底前）</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>立项与专班成立；确定 9/12 主日期与 9/9 备选；启动外事报批窗口沟通</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>综合协调组</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>T-45 天</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>锁定主会场与黑客松厂房；形成揭牌候选短名单；启动文脉短片脚本</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>文旅沉浸组</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>T-40 天</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>正式外事报批；东亚+东南亚 11 国总领事首轮邀约（按全部出席准备）；黑客松赛题与报名上线</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>外事礼宾组</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>T-30 天</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>确认至少 2 个国家厅+1 个片区厅意向；签约清单初稿；主视觉定稿</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>空间落位组</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>T-21 天</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>总领事确认过半、揭牌国本人锁定；分论坛嘉宾锁定；黑客松报名截止与初筛</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>T-14 天</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>全要素彩排脚本；揭牌铭牌进场；开放数据/API 包发给入围队伍</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>产业内容组</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>T-7 天</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>最终座次；同传联调；黑客松夜间值守与安全预案桌面推演</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>会务保障组</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>T-2 天</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>会场与工位布置完成；领导/领事行程再确认；演示设备验收</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>宣传媒体组</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>9/11 晚</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>黑客松开营</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>黑客松组</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>活动日 9/12</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>主会场+Demo Day+揭牌签约按议程执行</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>综合协调组</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>T+3 天</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>新闻通稿与短视频；领导汇报材料（一页纸+图文册）提交</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>宣传媒体组</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>T+14 天</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>会客厅运营启动会；黑客松优胜转化台账；复盘报告</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>文旅沉浸组</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4772,7 +5469,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>预算测算（示意，单位：万元）</t>
         </is>
@@ -4901,22 +5598,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>领事用车、休息室、伴手礼、翻译</t>
+          <t>按 11 国总领事全员预留：用车、休息室、伴手礼、翻译与位次</t>
         </is>
       </c>
     </row>
@@ -5144,22 +5841,22 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>中值约 70 万；场地/券包置换后现金可压至约 50 万</t>
+          <t>中值约 74 万；场地/券包置换后现金可压至约 50–55 万</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5189,7 +5886,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>预期成效与 KPI</t>
         </is>
@@ -5281,7 +5978,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>总领事亲自出席 ≥6 国；国际嘉宾可感知占比</t>
+          <t>东亚+东南亚按全部出席准备（约 11 国）；底线保障亲自出席 ≥6 国</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr"/>
@@ -5380,7 +6077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5396,7 +6093,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>风险预案</t>
         </is>
@@ -5486,7 +6183,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>扩大邀约池；揭牌国必须本人到场</t>
+          <t>按 11 国全覆盖邀约；揭牌国必须本人到场；未到场可派副总领事+书面致辞</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -5577,7 +6274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5593,9 +6290,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>下一步行动清单（主题定稿 · 企业锁定 · 敦煌核查）</t>
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>下一步行动清单（主题定稿 · 企业锁定 · 领事全名单邀约）</t>
         </is>
       </c>
     </row>
@@ -5767,7 +6464,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>10 日内：总领事邀约 + 黑客松报名上线 + 外事报批；敦煌达线则启动一事一议报区。</t>
+          <t>10 日内：东亚+东南亚总领事全名单邀约 + 黑客松报名上线 + 外事报批；敦煌达线则启动一事一议报区。</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -5810,7 +6507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5825,7 +6522,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>四大主题板块协同要点（含敦煌沉浸）</t>
         </is>
@@ -5940,7 +6637,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>四层结构：主论坛 · 分论坛 · 体验/游戏层 · 黑客松</t>
         </is>
@@ -6039,17 +6736,17 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>组合逻辑</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -6119,7 +6816,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>历史文脉时间轴 · 载体 · 衍生议题</t>
         </is>
@@ -6133,17 +6830,17 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>时期</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>节点</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>要点</t>
         </is>
@@ -6320,7 +7017,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>文脉载体</t>
         </is>
@@ -6429,7 +7126,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>衍生议题</t>
         </is>
@@ -6562,7 +7259,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>市、区领导寄托与活动回应</t>
         </is>
@@ -6855,7 +7552,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>大上海 / 杨浦规划对齐与六大课题</t>
         </is>
@@ -6988,17 +7685,17 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>课题编号</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>题目</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>聚焦内容</t>
         </is>
@@ -7132,7 +7829,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>「敦煌」文旅科技项目（意向落户）</t>
         </is>
@@ -7146,22 +7843,22 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>核实状态</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
@@ -7566,7 +8263,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>冷启动原则与协同角色</t>
         </is>
@@ -7687,17 +8384,17 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>角色方</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>价值与职责</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -7782,7 +8479,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>杨浦 AI / 具身智能优质企业互动清单</t>
         </is>
@@ -8093,17 +8790,17 @@
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>互动机制</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>责任方</t>
         </is>

--- a/deliverables/复兴岛_全球创客岛_科创出海与具身智能国际大会_执行计划表.xlsx
+++ b/deliverables/复兴岛_全球创客岛_科创出海与具身智能国际大会_执行计划表.xlsx
@@ -32,6 +32,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22.风险预案" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23.下一步行动" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24.主题板块" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25.出海行业支持" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1.活动总览'!$1:$4</definedName>
@@ -58,6 +59,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="22">'22.风险预案'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="23">'23.下一步行动'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="24">'24.主题板块'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="25">'25.出海行业支持'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -159,7 +161,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -181,80 +183,11 @@
         <color rgb="00D5DEEB"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D5DEEB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D5DEEB"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D5DEEB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D5DEEB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D5DEEB"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D5DEEB"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00D5DEEB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00D5DEEB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D5DEEB"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00D5DEEB"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -279,14 +212,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -670,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -689,7 +617,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>V3.2 · 建议稿｜杨浦AI企业互动｜四层结构｜敦煌意向｜主会日 2026-09-12</t>
+          <t>V3.3 · 建议稿｜杨浦AI企业互动｜四层结构｜敦煌意向｜主会日 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1411,28 +1339,86 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="48" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>23.下一步行动</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>企业锁定+领事全名单邀约</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>立即执行</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>24.主题板块</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>四大板块协同要点</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>内容统筹</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>25.出海行业支持</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>行业方向×当地支持×国别</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>领事圆桌专报</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="48" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>以百年「复兴」文脉与「敦煌」级文化 IP 为双引擎，以 9 月 15 日前收官节点为政治死线，在岛上以「主论坛 + 分论坛 + 沉浸式体验/游戏层 + 黑客松」组合拳，完成成果发布、国际会客厅揭牌与高价值项目（含敦煌意向）一事一议展示，形成可汇报、可传播、可复用的冷启动答卷。</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="12" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="13" t="n"/>
-      <c r="B40" s="14" t="n"/>
-      <c r="C40" s="14" t="n"/>
-      <c r="D40" s="15" t="n"/>
-    </row>
+    </row>
+    <row r="45"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A44:D45"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A39:D40"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1455,7 +1441,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>择日专章｜9/15 前最靠近收官节点的黄道吉日</t>
         </is>
@@ -1469,22 +1455,22 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>宜/要点</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>决策建议</t>
         </is>
@@ -1628,7 +1614,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>详细议程｜2026 年 9 月 12 日（星期六 · 农历八月初二）</t>
         </is>
@@ -2139,7 +2125,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>分国别对接桌：领事×出海企业</t>
+          <t>国别分桌：行业方向×当地支持（见领事专报）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2371,7 +2357,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>体验 / 游戏层关卡设计（论坛×游戏化体验）</t>
         </is>
@@ -2564,7 +2550,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>「船台·智能体」复兴创客黑客松｜执行台账</t>
         </is>
@@ -2578,22 +2564,22 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -3176,7 +3162,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>嘉宾分层与邀约目标（含杨浦企业主力军）</t>
         </is>
@@ -3330,7 +3316,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>东亚 + 东南亚驻沪总领事名单（暂按全部出席准备）</t>
         </is>
@@ -3344,7 +3330,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>策划口径：席位/用车/伴手礼/同传按 11 国全员预留；正式出席以外事书面确认为准。</t>
         </is>
@@ -3833,35 +3819,35 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>暂未在沪设总领事馆（不纳入本场全员预留，一事一议）</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>· 缅甸：目前未在上海设总领事馆；领事事务多由驻华使馆或驻昆明/南宁/重庆总领馆等办理</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>· 文莱：目前未在上海设总领事馆；对华事务由驻华大使馆统筹</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>· 朝鲜：驻沪总领事馆已于历史上闭馆；现有驻华机构主要为驻华使馆及驻沈阳总领馆等</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>· 东帝汶：目前未见驻沪总领事馆公开信息；涉及合作可一事一议协调使馆层面</t>
         </is>
@@ -3901,7 +3887,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>拟邀「一带一路」延伸国家参考池（中东/中亚/中东欧）</t>
         </is>
@@ -4266,7 +4252,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>国际会议厅 / 会客厅揭牌落位计划（含敦煌视进度）</t>
         </is>
@@ -4417,42 +4403,42 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>落位原则</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>· 先锁意向、再上仪式：揭牌对象须在活动前完成协议文本与空间确认。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>· 一国一厅、一厅一责：明确运营主体、年度活动频次与招商指标。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>· 外事合规：领事出席与冠名事项提前报区外办 / 市外办指导。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>· 文脉同框：揭牌背景尽量融入船台/塔吊/老厂房元素，形成独特视觉记忆。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>· 媒体可感知：揭牌背板、铭牌、导视与文脉短片同步备妥。</t>
         </is>
@@ -4488,7 +4474,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>席位结构（主会场 200–300 人）</t>
         </is>
@@ -4695,7 +4681,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>组织架构与职责（含智库/文旅/黑客松）</t>
         </is>
@@ -4916,7 +4902,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>创客复兴·智汇杨浦｜活动总览</t>
         </is>
@@ -5110,7 +5096,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>执行倒排期</t>
         </is>
@@ -5469,7 +5455,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>预算测算（示意，单位：万元）</t>
         </is>
@@ -5886,7 +5872,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>预期成效与 KPI</t>
         </is>
@@ -6093,7 +6079,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>风险预案</t>
         </is>
@@ -6290,7 +6276,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>下一步行动清单（主题定稿 · 企业锁定 · 领事全名单邀约）</t>
         </is>
@@ -6522,7 +6508,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>四大主题板块协同要点（含敦煌沉浸）</t>
         </is>
@@ -6616,6 +6602,662 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>复兴岛出海企业行业方向与当地支持诉求｜领事对接专报｜让总领事有的放矢回答与协调</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>供分论坛 C 国别分桌与总领事会前预读；正式口径以外事确认为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>代号</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>行业方向</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>代表企业</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>出海计划</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>优先市场</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>当地支持诉求</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>总领事可如何帮助</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>智算云与数据基础设施</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>优刻得、道客网络</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>区域云节点 / 算力调度 / 政企上云与出海企业「伴生云」服务</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>新加坡、马来西亚、泰国、印尼</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>数据本地化与跨境传输合规路径解读（PDPA 等）；机房/电力/土地审批与绿色电力对接窗口；主权云、政务云、电信运营商合作引荐；本地 IDC、系统集成商与法务合规律所清单</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>推荐合规顾问与运营商；协调投资促进机构见洽；说明数据中心能耗政策</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>大模型与行业智能应用</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>智谱 AI、声网 Agora</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>行业大模型 API、智能体、实时互动/同传与本地化 SaaS 落地</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>新加坡、越南、印尼、泰国、马来西亚</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>AI 内容/伦理监管与行业准入口径说明；本地语言语料、高校/科研院所合作对接；政企、金融、教育等可试点项目清单；云分发、支付、应用商店与渠道伙伴引荐</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>介绍数字经济主管部门；牵线行业协会与标杆政企客户；澄清敏感应用边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>具身智能与智能制造装备</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>苏度、卓益得、傲鲨、清宝引擎</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>工业/康养外骨骼、人形机器人示范产线、培训与售后本地化</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>日本、韩国、越南、泰国、马来西亚、印尼</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>进出口、安全与电磁等认证路径（含检测机构）；工业园区示范线、仓储物流与康养场景试点；本地代理、系统集成与售后服务伙伴；技能培训、展会采购团与关税优惠政策解读</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>对接工业园/BOI 类机构；推荐认证实验室；组织买家与渠道见面</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>智能终端与物理 AI 商业场景</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>商米科技</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>智能收银/终端 + AI 店务，服务本地零售餐饮连锁扩张</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>东南亚重点市场；日韩渠道协同</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>零售/餐饮头部连锁与经销商名录；清关、关税与本地售后仓储便利化建议；本地支付、发票财税合规合作伙伴；品牌保护、知识产权与打假协同渠道</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>引荐商协会与连锁总部；说明消费电子进口要点；协调展会摊位资源</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>低空经济与城市无人系统</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>美团无人机（场景方）及生态伙伴</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>城市物流试飞、景区/园区低空应用与标准互认探讨</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>新加坡、日本、韩国、马来西亚、泰国</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>空域法规、试飞许可与保险要求解读；可开放示范航线/园区场景清单；本地运营商、机场/物流枢纽合作接口；应急、公安与城管协同机制说明</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>介绍民航/交通主管部门窗口；协助申请观摩或试点对接；提示禁飞红线</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>文旅科技与沉浸体验</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>敦煌文旅科技意向方；声网等实时互动协同</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>沉浸展陈、机器人导览、文旅数字化产品区域复制</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>泰国、新加坡、日本、韩国、印尼</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>文旅主管部门与头部景区/博物馆对接；IP 授权、内容审查与演出展陈合规指引；本地运营 integrators 与场馆空间资源；旅游投资促进与联合推广活动机会</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>牵线文旅局与标杆场馆；说明内容审查要点；推荐本地运营伙伴</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>国别×优先行业匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>国家</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>总领事</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>优先对接行业</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>会谈切入点</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>陈子勤</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>智算云、大模型、低空、文旅</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>总部/合规/金融科技枢纽；优先谈数据合规与区域总部</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>马来西亚</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>沙哈菲兹·沙哈里斯</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>智算云、具身制造、智能终端</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>数据中心与电子制造；电力土地与 BOI 类激励</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>陈佩恩</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>智算云、具身、智能终端、文旅</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>智能制造+消费市场；EEC/投资促进与文旅场景</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>印尼</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>邯伯盼</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>智算云、大模型、具身、智能终端</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>人口与消费市场；本地化运营与渠道为先</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>陈辉雄</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>大模型应用、具身制造、智能终端</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>电子制造与供应链；工厂自动化与培训</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>菲律宾</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>方明易</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>大模型应用、智能终端、文旅</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>BPO/数字服务与消费场景；渠道与人才</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>宁维斯</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>智能终端、具身轻应用、文旅</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>产能合作与基建配套；务实项目制对接</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>老挝</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>维达万·桥本控</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>智能终端、文旅、通道物流</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>中老铁路沿线经贸与人文场景</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>冈田胜</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>具身智能、低空、大模型行业应用</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>高端制造与康养；认证标准与示范产线</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>韩国</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>金英俊</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>具身、智能终端、大模型应用</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>消费电子与文创；渠道与技术标准协同</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>蒙古国</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>道尔吉德日木·宝勒德</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>智算轻应用、通道与资源数字化</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>教育人文+跨境通道；量力务实项目</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>支持五包</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>· 合规准入包：数据本地化、AI 伦理、产品认证、进出口与关税、内容审查</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>· 资源对接包：工业园/BOI、运营商、连锁渠道、景区场馆、高校科研</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>· 场景试点包：政企试点、示范产线、试飞航线、沉浸展陈落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>· 伙伴撮合包：代理商、集成商、律所、保险、本地运维团队</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>· 活动赋能包：本国展会摊位、采购代表团、联合推介与媒体背书</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -6637,7 +7279,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>四层结构：主论坛 · 分论坛 · 体验/游戏层 · 黑客松</t>
         </is>
@@ -6736,17 +7378,17 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>组合逻辑</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -6816,7 +7458,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>历史文脉时间轴 · 载体 · 衍生议题</t>
         </is>
@@ -6830,17 +7472,17 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>时期</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>节点</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>要点</t>
         </is>
@@ -7017,7 +7659,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>文脉载体</t>
         </is>
@@ -7126,7 +7768,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>衍生议题</t>
         </is>
@@ -7259,7 +7901,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>市、区领导寄托与活动回应</t>
         </is>
@@ -7552,7 +8194,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>大上海 / 杨浦规划对齐与六大课题</t>
         </is>
@@ -7685,17 +8327,17 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>课题编号</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>题目</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>聚焦内容</t>
         </is>
@@ -7829,7 +8471,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>「敦煌」文旅科技项目（意向落户）</t>
         </is>
@@ -7843,22 +8485,22 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>核实状态</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
@@ -8263,7 +8905,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>冷启动原则与协同角色</t>
         </is>
@@ -8384,17 +9026,17 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>角色方</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>价值与职责</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -8479,7 +9121,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>杨浦 AI / 具身智能优质企业互动清单</t>
         </is>
@@ -8790,17 +9432,17 @@
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>互动机制</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>责任方</t>
         </is>
